--- a/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
+++ b/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Sambar deer Coefs" sheetId="5" r:id="rId5"/>
     <sheet name="Gaur Coefs" sheetId="6" r:id="rId6"/>
     <sheet name="Muntjac Coefs" sheetId="7" r:id="rId7"/>
+    <sheet name="Wild boar Coefs" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -649,41 +650,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Individual Density (ind/km2)</t>
+          <t>Cluster Density (groups/km2)</t>
         </is>
       </c>
       <c r="C6">
-        <v>2.99620119269927</v>
+        <v>2.55626240277563</v>
       </c>
       <c r="D6">
-        <v>0.6759069869866315</v>
+        <v>0.3022206207288703</v>
+      </c>
+      <c r="E6">
+        <v>0.06983059509814639</v>
       </c>
       <c r="F6">
-        <v>2.99620119269927</v>
+        <v>2.491116456417281</v>
       </c>
       <c r="G6">
-        <v>2.19645673661991</v>
+        <v>2.100254030573951</v>
       </c>
       <c r="H6">
-        <v>2.301493628775776</v>
+        <v>2.154840313026877</v>
+      </c>
+      <c r="I6">
+        <v>2.222009531269085</v>
       </c>
       <c r="J6">
-        <v>2.682319484836729</v>
+        <v>2.328408091658141</v>
       </c>
       <c r="K6">
-        <v>2.99620119269927</v>
+        <v>2.491116456417281</v>
       </c>
       <c r="L6">
-        <v>3.39459422898263</v>
+        <v>2.74722512276364</v>
       </c>
       <c r="M6">
-        <v>4.236671823571405</v>
+        <v>2.956300140330133</v>
       </c>
       <c r="N6">
-        <v>4.236671823571405</v>
+        <v>3.169591038275269</v>
       </c>
       <c r="O6">
-        <v>4.846012125607506</v>
+        <v>3.274075544338432</v>
       </c>
     </row>
     <row r="7">
@@ -694,47 +701,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Total Individual Abundance</t>
+          <t>Total Cluster Abundance</t>
         </is>
       </c>
       <c r="C7">
-        <v>9021.5617912175</v>
+        <v>7696.906094757423</v>
       </c>
       <c r="D7">
-        <v>2035.155937816748</v>
+        <v>909.9862890146287</v>
+      </c>
+      <c r="E7">
+        <v>210.2599218405193</v>
       </c>
       <c r="F7">
-        <v>9021.5617912175</v>
+        <v>7500.751650272432</v>
       </c>
       <c r="G7">
-        <v>6613.53123396255</v>
+        <v>6323.864886058167</v>
       </c>
       <c r="H7">
-        <v>6929.79731624386</v>
+        <v>6488.224182523926</v>
+      </c>
+      <c r="I7">
+        <v>6690.470698651216</v>
       </c>
       <c r="J7">
-        <v>8076.46396884339</v>
+        <v>7010.836763982662</v>
       </c>
       <c r="K7">
-        <v>9021.5617912175</v>
+        <v>7500.751650272432</v>
       </c>
       <c r="L7">
-        <v>10221.1232234667</v>
+        <v>8271.894844641321</v>
       </c>
       <c r="M7">
-        <v>12756.6188607735</v>
+        <v>8901.419722534029</v>
       </c>
       <c r="N7">
-        <v>12756.6188607735</v>
+        <v>9543.638616246835</v>
       </c>
       <c r="O7">
-        <v>14591.3425102042</v>
+        <v>9858.241464003018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gaur</t>
+          <t>Sambar deer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -743,43 +756,49 @@
         </is>
       </c>
       <c r="C8">
-        <v>1.24035283911446</v>
+        <v>2.971094459366412</v>
       </c>
       <c r="D8">
-        <v>1.655999486482059</v>
+        <v>0.3512651951453976</v>
+      </c>
+      <c r="E8">
+        <v>0.08116275307460004</v>
       </c>
       <c r="F8">
-        <v>1.24035283911446</v>
+        <v>2.895376583116576</v>
       </c>
       <c r="G8">
-        <v>0.5761435073623314</v>
+        <v>2.44108472851797</v>
       </c>
       <c r="H8">
-        <v>0.6407251293166789</v>
+        <v>2.504529311193519</v>
+      </c>
+      <c r="I8">
+        <v>2.582598797308367</v>
       </c>
       <c r="J8">
-        <v>0.9256563966350979</v>
+        <v>2.706263790743014</v>
       </c>
       <c r="K8">
-        <v>1.24035283911446</v>
+        <v>2.895376583116576</v>
       </c>
       <c r="L8">
-        <v>1.74137406518174</v>
+        <v>3.193046743563003</v>
       </c>
       <c r="M8">
-        <v>3.888511739484158</v>
+        <v>3.436050601699496</v>
       </c>
       <c r="N8">
-        <v>3.888511739484158</v>
+        <v>3.683954496240993</v>
       </c>
       <c r="O8">
-        <v>7.067661494372002</v>
+        <v>3.805394821270546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gaur</t>
+          <t>Sambar deer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -788,133 +807,151 @@
         </is>
       </c>
       <c r="C9">
-        <v>3734.70239857364</v>
+        <v>8945.965417152267</v>
       </c>
       <c r="D9">
-        <v>4986.214453797479</v>
+        <v>1057.659502582792</v>
+      </c>
+      <c r="E9">
+        <v>244.3810495076208</v>
       </c>
       <c r="F9">
-        <v>3734.70239857364</v>
+        <v>8717.978891764011</v>
       </c>
       <c r="G9">
-        <v>1734.76810066798</v>
+        <v>7350.106117567606</v>
       </c>
       <c r="H9">
-        <v>1929.22336437252</v>
+        <v>7541.137756003685</v>
+      </c>
+      <c r="I9">
+        <v>7776.204978695492</v>
       </c>
       <c r="J9">
-        <v>2787.15141026828</v>
+        <v>8148.560273927216</v>
       </c>
       <c r="K9">
-        <v>3734.70239857364</v>
+        <v>8717.978891764011</v>
       </c>
       <c r="L9">
-        <v>5243.27731026222</v>
+        <v>9614.263744868204</v>
       </c>
       <c r="M9">
-        <v>11708.3088475868</v>
+        <v>10345.94836171718</v>
       </c>
       <c r="N9">
-        <v>11708.3088475868</v>
+        <v>11092.38698818163</v>
       </c>
       <c r="O9">
-        <v>21280.7287595541</v>
+        <v>11458.04380684561</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muntjac</t>
+          <t>Gaur</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Individual Density (ind/km2)</t>
+          <t>Cluster Density (groups/km2)</t>
         </is>
       </c>
       <c r="C10">
-        <v>4.907018146113352</v>
+        <v>0.5736475454187102</v>
       </c>
       <c r="D10">
-        <v>0.4654697978778156</v>
+        <v>0.2387013083098297</v>
+      </c>
+      <c r="E10">
+        <v>0.005812783119923934</v>
       </c>
       <c r="F10">
-        <v>4.907018146113352</v>
+        <v>0.5269085563469562</v>
       </c>
       <c r="G10">
-        <v>4.091282661287213</v>
+        <v>0.3019083821100759</v>
       </c>
       <c r="H10">
-        <v>4.204829984447957</v>
+        <v>0.3268068776474342</v>
+      </c>
+      <c r="I10">
+        <v>0.3613767671752686</v>
       </c>
       <c r="J10">
-        <v>4.611327463838028</v>
+        <v>0.4322242877187489</v>
       </c>
       <c r="K10">
-        <v>4.907018146113352</v>
+        <v>0.5269085563469562</v>
       </c>
       <c r="L10">
-        <v>5.237394397358818</v>
+        <v>0.6511376255298309</v>
       </c>
       <c r="M10">
-        <v>5.738923984431385</v>
+        <v>0.8164374566539205</v>
       </c>
       <c r="N10">
-        <v>5.738923984431385</v>
+        <v>0.9480886790985036</v>
       </c>
       <c r="O10">
-        <v>5.91592426896825</v>
+        <v>1.120504454935139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muntjac</t>
+          <t>Gaur</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total Individual Abundance</t>
+          <t>Total Cluster Abundance</t>
         </is>
       </c>
       <c r="C11">
-        <v>14775.0316379473</v>
+        <v>1727.252759255736</v>
       </c>
       <c r="D11">
-        <v>1401.529561410103</v>
+        <v>718.7296393208971</v>
+      </c>
+      <c r="E11">
+        <v>17.50228997409096</v>
       </c>
       <c r="F11">
-        <v>14775.0316379473</v>
+        <v>1586.521663160685</v>
       </c>
       <c r="G11">
-        <v>12318.8520931358</v>
+        <v>909.0461385334387</v>
       </c>
       <c r="H11">
-        <v>12660.7430831728</v>
+        <v>984.0155085964242</v>
+      </c>
+      <c r="I11">
+        <v>1088.105445964734</v>
       </c>
       <c r="J11">
-        <v>13884.7069936163</v>
+        <v>1301.427330321153</v>
       </c>
       <c r="K11">
-        <v>14775.0316379473</v>
+        <v>1586.521663160685</v>
       </c>
       <c r="L11">
-        <v>15769.7945304474</v>
+        <v>1960.575390470321</v>
       </c>
       <c r="M11">
-        <v>17279.9001171229</v>
+        <v>2458.293181984955</v>
       </c>
       <c r="N11">
-        <v>17279.9001171229</v>
+        <v>2854.695012765595</v>
       </c>
       <c r="O11">
-        <v>17812.8479738634</v>
+        <v>3373.838913809704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wild boar</t>
+          <t>Gaur</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -923,82 +960,502 @@
         </is>
       </c>
       <c r="C12">
-        <v>1.924371988151906</v>
+        <v>0.9434916568226003</v>
       </c>
       <c r="D12">
-        <v>0.7664371818267145</v>
+        <v>0.3949175644423798</v>
+      </c>
+      <c r="E12">
+        <v>0.009817211393865903</v>
       </c>
       <c r="F12">
-        <v>1.924371988151906</v>
+        <v>0.8641347683795145</v>
       </c>
       <c r="G12">
-        <v>1.088424520385111</v>
+        <v>0.4924670843997955</v>
       </c>
       <c r="H12">
-        <v>1.183672015490571</v>
+        <v>0.5342393312260267</v>
+      </c>
+      <c r="I12">
+        <v>0.5921058963894842</v>
       </c>
       <c r="J12">
-        <v>1.564221818360847</v>
+        <v>0.7069900615092062</v>
       </c>
       <c r="K12">
-        <v>1.924371988151906</v>
+        <v>0.8641347683795145</v>
       </c>
       <c r="L12">
-        <v>2.40715902920256</v>
+        <v>1.07580760839935</v>
       </c>
       <c r="M12">
-        <v>3.58845131335729</v>
+        <v>1.343715433989869</v>
       </c>
       <c r="N12">
-        <v>3.58845131335729</v>
+        <v>1.580033525745385</v>
       </c>
       <c r="O12">
-        <v>4.092858273145832</v>
+        <v>1.864521766010666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Gaur</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Total Individual Abundance</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>2840.853378692849</v>
+      </c>
+      <c r="D13">
+        <v>1189.096786536006</v>
+      </c>
+      <c r="E13">
+        <v>29.55962350693015</v>
+      </c>
+      <c r="F13">
+        <v>2601.909787590718</v>
+      </c>
+      <c r="G13">
+        <v>1482.818391127784</v>
+      </c>
+      <c r="H13">
+        <v>1608.594626321567</v>
+      </c>
+      <c r="I13">
+        <v>1782.830854028737</v>
+      </c>
+      <c r="J13">
+        <v>2128.74707520422</v>
+      </c>
+      <c r="K13">
+        <v>2601.909787590718</v>
+      </c>
+      <c r="L13">
+        <v>3239.256708890442</v>
+      </c>
+      <c r="M13">
+        <v>4045.927171743496</v>
+      </c>
+      <c r="N13">
+        <v>4757.480946019355</v>
+      </c>
+      <c r="O13">
+        <v>5614.075037458117</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cluster Density (groups/km2)</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>3.302138719202004</v>
+      </c>
+      <c r="D14">
+        <v>0.3105836706421144</v>
+      </c>
+      <c r="E14">
+        <v>0.01049747475833203</v>
+      </c>
+      <c r="F14">
+        <v>3.29221870689546</v>
+      </c>
+      <c r="G14">
+        <v>2.731993594118687</v>
+      </c>
+      <c r="H14">
+        <v>2.81437071525446</v>
+      </c>
+      <c r="I14">
+        <v>2.908552962757267</v>
+      </c>
+      <c r="J14">
+        <v>3.084605857518146</v>
+      </c>
+      <c r="K14">
+        <v>3.29221870689546</v>
+      </c>
+      <c r="L14">
+        <v>3.505734733031819</v>
+      </c>
+      <c r="M14">
+        <v>3.705483611686945</v>
+      </c>
+      <c r="N14">
+        <v>3.820060787366249</v>
+      </c>
+      <c r="O14">
+        <v>3.939580295845329</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Total Cluster Abundance</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>9942.739683517235</v>
+      </c>
+      <c r="D15">
+        <v>935.1674323034065</v>
+      </c>
+      <c r="E15">
+        <v>31.60789649733783</v>
+      </c>
+      <c r="F15">
+        <v>9912.870526462231</v>
+      </c>
+      <c r="G15">
+        <v>8226.032711891366</v>
+      </c>
+      <c r="H15">
+        <v>8474.070223631179</v>
+      </c>
+      <c r="I15">
+        <v>8757.652970862131</v>
+      </c>
+      <c r="J15">
+        <v>9287.748236987136</v>
+      </c>
+      <c r="K15">
+        <v>9912.870526462231</v>
+      </c>
+      <c r="L15">
+        <v>10555.76728115881</v>
+      </c>
+      <c r="M15">
+        <v>11157.21115478939</v>
+      </c>
+      <c r="N15">
+        <v>11502.20303075978</v>
+      </c>
+      <c r="O15">
+        <v>11862.07627079029</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Individual Density (ind/km2)</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>5.288630147728718</v>
+      </c>
+      <c r="D16">
+        <v>0.5064812398813096</v>
+      </c>
+      <c r="E16">
+        <v>0.0169093308874078</v>
+      </c>
+      <c r="F16">
+        <v>5.268500562841703</v>
+      </c>
+      <c r="G16">
+        <v>4.372666986522947</v>
+      </c>
+      <c r="H16">
+        <v>4.494598370676053</v>
+      </c>
+      <c r="I16">
+        <v>4.649256866482665</v>
+      </c>
+      <c r="J16">
+        <v>4.93477344524511</v>
+      </c>
+      <c r="K16">
+        <v>5.268500562841703</v>
+      </c>
+      <c r="L16">
+        <v>5.617024069249879</v>
+      </c>
+      <c r="M16">
+        <v>5.944131067507745</v>
+      </c>
+      <c r="N16">
+        <v>6.14905115458347</v>
+      </c>
+      <c r="O16">
+        <v>6.325148292017036</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total Individual Abundance</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>15924.06537481117</v>
+      </c>
+      <c r="D17">
+        <v>1525.015013282623</v>
+      </c>
+      <c r="E17">
+        <v>50.91399530198451</v>
+      </c>
+      <c r="F17">
+        <v>15863.45519471637</v>
+      </c>
+      <c r="G17">
+        <v>13166.10029642059</v>
+      </c>
+      <c r="H17">
+        <v>13533.2356941056</v>
+      </c>
+      <c r="I17">
+        <v>13998.9124249793</v>
+      </c>
+      <c r="J17">
+        <v>14858.60284363303</v>
+      </c>
+      <c r="K17">
+        <v>15863.45519471637</v>
+      </c>
+      <c r="L17">
+        <v>16912.85947251139</v>
+      </c>
+      <c r="M17">
+        <v>17897.77864426582</v>
+      </c>
+      <c r="N17">
+        <v>18514.79302645082</v>
+      </c>
+      <c r="O17">
+        <v>19045.0215072633</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Wild boar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cluster Density (groups/km2)</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>1.066772048431813</v>
+      </c>
+      <c r="D18">
+        <v>0.2971928781405579</v>
+      </c>
+      <c r="E18">
+        <v>0.04475377625919544</v>
+      </c>
+      <c r="F18">
+        <v>1.045946220946593</v>
+      </c>
+      <c r="G18">
+        <v>0.6063857188295807</v>
+      </c>
+      <c r="H18">
+        <v>0.6524898886976535</v>
+      </c>
+      <c r="I18">
+        <v>0.7214589139477691</v>
+      </c>
+      <c r="J18">
+        <v>0.8480871787829755</v>
+      </c>
+      <c r="K18">
+        <v>1.045946220946593</v>
+      </c>
+      <c r="L18">
+        <v>1.224853944653267</v>
+      </c>
+      <c r="M18">
+        <v>1.463544908904735</v>
+      </c>
+      <c r="N18">
+        <v>1.590906638833788</v>
+      </c>
+      <c r="O18">
+        <v>1.732996218201568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total Cluster Abundance</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>3212.050637828188</v>
+      </c>
+      <c r="D19">
+        <v>894.84775608122</v>
+      </c>
+      <c r="E19">
+        <v>134.7536203164374</v>
+      </c>
+      <c r="F19">
+        <v>3149.344071270192</v>
+      </c>
+      <c r="G19">
+        <v>1825.827399395867</v>
+      </c>
+      <c r="H19">
+        <v>1964.647054868635</v>
+      </c>
+      <c r="I19">
+        <v>2172.312789896733</v>
+      </c>
+      <c r="J19">
+        <v>2553.590495315539</v>
+      </c>
+      <c r="K19">
+        <v>3149.344071270192</v>
+      </c>
+      <c r="L19">
+        <v>3688.035227350986</v>
+      </c>
+      <c r="M19">
+        <v>4406.733720712157</v>
+      </c>
+      <c r="N19">
+        <v>4790.219889528536</v>
+      </c>
+      <c r="O19">
+        <v>5218.051613004921</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Individual Density (ind/km2)</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>2.116056030495891</v>
+      </c>
+      <c r="D20">
+        <v>0.5895137418853691</v>
+      </c>
+      <c r="E20">
+        <v>0.0887738840551253</v>
+      </c>
+      <c r="F20">
+        <v>2.074745782533406</v>
+      </c>
+      <c r="G20">
+        <v>1.202830688170152</v>
+      </c>
+      <c r="H20">
+        <v>1.294283221842886</v>
+      </c>
+      <c r="I20">
+        <v>1.431090632584919</v>
+      </c>
+      <c r="J20">
+        <v>1.682271289061312</v>
+      </c>
+      <c r="K20">
+        <v>2.074745782533406</v>
+      </c>
+      <c r="L20">
+        <v>2.429628316443365</v>
+      </c>
+      <c r="M20">
+        <v>2.903097278319228</v>
+      </c>
+      <c r="N20">
+        <v>3.155732840965384</v>
+      </c>
+      <c r="O20">
+        <v>3.437582662334257</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Total Individual Abundance</t>
         </is>
       </c>
-      <c r="C13">
-        <v>5794.28405632539</v>
-      </c>
-      <c r="D13">
-        <v>2307.742354480237</v>
-      </c>
-      <c r="F13">
-        <v>5794.28405632539</v>
-      </c>
-      <c r="G13">
-        <v>3277.24623087957</v>
-      </c>
-      <c r="H13">
-        <v>3564.03643864211</v>
-      </c>
-      <c r="J13">
-        <v>4709.87189508451</v>
-      </c>
-      <c r="K13">
-        <v>5794.28405632539</v>
-      </c>
-      <c r="L13">
-        <v>7247.95583692891</v>
-      </c>
-      <c r="M13">
-        <v>10804.8269045188</v>
-      </c>
-      <c r="N13">
-        <v>10804.8269045188</v>
-      </c>
-      <c r="O13">
-        <v>12323.5962604421</v>
+      <c r="C21">
+        <v>6371.444707823127</v>
+      </c>
+      <c r="D21">
+        <v>1775.025876816846</v>
+      </c>
+      <c r="E21">
+        <v>267.2981648899822</v>
+      </c>
+      <c r="F21">
+        <v>6247.059551208086</v>
+      </c>
+      <c r="G21">
+        <v>3621.723202080327</v>
+      </c>
+      <c r="H21">
+        <v>3897.086780968931</v>
+      </c>
+      <c r="I21">
+        <v>4309.013894713191</v>
+      </c>
+      <c r="J21">
+        <v>5065.318851363611</v>
+      </c>
+      <c r="K21">
+        <v>6247.059551208086</v>
+      </c>
+      <c r="L21">
+        <v>7315.610860810972</v>
+      </c>
+      <c r="M21">
+        <v>8741.225905019197</v>
+      </c>
+      <c r="N21">
+        <v>9501.91158414677</v>
+      </c>
+      <c r="O21">
+        <v>10350.56139628845</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2470,41 +2927,47 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_ndvi_cv</t>
         </is>
       </c>
       <c r="H21">
-        <v>-1.77550211362218</v>
+        <v>0.8337359854465328</v>
+      </c>
+      <c r="I21">
+        <v>0.7380390476713603</v>
+      </c>
+      <c r="J21">
+        <v>0.02844388581785389</v>
       </c>
       <c r="K21">
-        <v>-1.77550211362218</v>
+        <v>0.9230883691996279</v>
       </c>
       <c r="L21">
-        <v>-2.92805228954337</v>
+        <v>-1.342559700887139</v>
       </c>
       <c r="M21">
-        <v>-2.68365474742128</v>
+        <v>-0.5293593826140167</v>
       </c>
       <c r="N21">
-        <v>-2.42720851528167</v>
+        <v>0.1992485863476329</v>
       </c>
       <c r="O21">
-        <v>-2.08805416610993</v>
+        <v>0.5882405310485335</v>
       </c>
       <c r="P21">
-        <v>-1.77550211362218</v>
+        <v>0.9230883691996279</v>
       </c>
       <c r="Q21">
-        <v>-1.45487540780859</v>
+        <v>1.221989431438493</v>
       </c>
       <c r="R21">
-        <v>-1.15334022064003</v>
+        <v>1.504887118970426</v>
       </c>
       <c r="S21">
-        <v>-0.991704409058911</v>
+        <v>1.713008515343956</v>
       </c>
       <c r="T21">
-        <v>-0.889084701812326</v>
+        <v>1.91663993128164</v>
       </c>
     </row>
     <row r="22">
@@ -2534,41 +2997,47 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H22">
-        <v>1.12540019655818</v>
+        <v>-0.3806288059268695</v>
+      </c>
+      <c r="I22">
+        <v>1.136733883711535</v>
+      </c>
+      <c r="J22">
+        <v>0.02995669114975803</v>
       </c>
       <c r="K22">
-        <v>1.12540019655818</v>
+        <v>-0.5821611307596413</v>
       </c>
       <c r="L22">
-        <v>0.206790378027343</v>
+        <v>-2.376804979109037</v>
       </c>
       <c r="M22">
-        <v>0.328674427925573</v>
+        <v>-1.873883017290939</v>
       </c>
       <c r="N22">
-        <v>0.48026954239893</v>
+        <v>-1.509770142132372</v>
       </c>
       <c r="O22">
-        <v>0.7728398604873939</v>
+        <v>-1.035017637596761</v>
       </c>
       <c r="P22">
-        <v>1.12540019655818</v>
+        <v>-0.5821611307596413</v>
       </c>
       <c r="Q22">
-        <v>1.43801732597714</v>
+        <v>0.05298732917228682</v>
       </c>
       <c r="R22">
-        <v>1.79491255631904</v>
+        <v>1.213978036728389</v>
       </c>
       <c r="S22">
-        <v>2.06651009407335</v>
+        <v>1.912291546120434</v>
       </c>
       <c r="T22">
-        <v>2.32491558042549</v>
+        <v>2.429291883239949</v>
       </c>
     </row>
     <row r="23">
@@ -2598,41 +3067,47 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H23">
-        <v>-0.285354992876321</v>
+        <v>0.6229935946048304</v>
+      </c>
+      <c r="I23">
+        <v>0.9488182407534228</v>
+      </c>
+      <c r="J23">
+        <v>0.032185399299025</v>
       </c>
       <c r="K23">
-        <v>-0.285354992876321</v>
+        <v>0.7849902698081848</v>
       </c>
       <c r="L23">
-        <v>-1.20933735478135</v>
+        <v>-2.115349662222658</v>
       </c>
       <c r="M23">
-        <v>-1.07691701560579</v>
+        <v>-1.385249644667364</v>
       </c>
       <c r="N23">
-        <v>-0.915513828747217</v>
+        <v>-0.4937873193970266</v>
       </c>
       <c r="O23">
-        <v>-0.603673786409283</v>
+        <v>0.4185501645629774</v>
       </c>
       <c r="P23">
-        <v>-0.285354992876321</v>
+        <v>0.7849902698081848</v>
       </c>
       <c r="Q23">
-        <v>0.00776062855076141</v>
+        <v>1.098737734738604</v>
       </c>
       <c r="R23">
-        <v>0.272561540916779</v>
+        <v>1.398122505638628</v>
       </c>
       <c r="S23">
-        <v>0.416080160200481</v>
+        <v>1.635025216621362</v>
       </c>
       <c r="T23">
-        <v>0.544822185744366</v>
+        <v>2.138885356616776</v>
       </c>
     </row>
     <row r="24">
@@ -2642,7 +3117,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2651,52 +3126,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + DE</t>
+          <t>ndvi_cv + elev + BB + DE</t>
         </is>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F24">
-        <v>0.661</v>
+        <v>0.296</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>beta_DE</t>
+          <t>beta_ndvi_cv</t>
         </is>
       </c>
       <c r="H24">
-        <v>1.05065352262729</v>
+        <v>0.8002416545302975</v>
+      </c>
+      <c r="I24">
+        <v>0.7700066559454261</v>
+      </c>
+      <c r="J24">
+        <v>0.03204582605609804</v>
       </c>
       <c r="K24">
-        <v>1.05065352262729</v>
+        <v>0.9047760017188051</v>
       </c>
       <c r="L24">
-        <v>0.217460982256379</v>
+        <v>-1.514767739662864</v>
       </c>
       <c r="M24">
-        <v>0.355591419265951</v>
+        <v>-0.7262525901310021</v>
       </c>
       <c r="N24">
-        <v>0.513018823524845</v>
+        <v>0.165906721491429</v>
       </c>
       <c r="O24">
-        <v>0.766116846187338</v>
+        <v>0.5886160595071621</v>
       </c>
       <c r="P24">
-        <v>1.05065352262729</v>
+        <v>0.9047760017188051</v>
       </c>
       <c r="Q24">
-        <v>1.32511787072351</v>
+        <v>1.193656752042501</v>
       </c>
       <c r="R24">
-        <v>1.56909143123296</v>
+        <v>1.482927105977661</v>
       </c>
       <c r="S24">
-        <v>1.73400215757066</v>
+        <v>1.674904271739513</v>
       </c>
       <c r="T24">
-        <v>1.87544188930189</v>
+        <v>1.883553567924814</v>
       </c>
     </row>
     <row r="25">
@@ -2726,41 +3207,47 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H25">
-        <v>-1.92829098084159</v>
+        <v>-0.4516004966752659</v>
+      </c>
+      <c r="I25">
+        <v>1.108418499790955</v>
+      </c>
+      <c r="J25">
+        <v>0.03351978242951942</v>
       </c>
       <c r="K25">
-        <v>-1.92829098084159</v>
+        <v>-0.6277626170031898</v>
       </c>
       <c r="L25">
-        <v>-3.08733105521218</v>
+        <v>-2.426078291355212</v>
       </c>
       <c r="M25">
-        <v>-2.88933847760348</v>
+        <v>-1.960354953096786</v>
       </c>
       <c r="N25">
-        <v>-2.6530236126615</v>
+        <v>-1.570689684543826</v>
       </c>
       <c r="O25">
-        <v>-2.28982282453145</v>
+        <v>-1.067519594187461</v>
       </c>
       <c r="P25">
-        <v>-1.92829098084159</v>
+        <v>-0.6277626170031898</v>
       </c>
       <c r="Q25">
-        <v>-1.6042154412775</v>
+        <v>-0.004170207489960706</v>
       </c>
       <c r="R25">
-        <v>-1.32061197355128</v>
+        <v>1.061512540448699</v>
       </c>
       <c r="S25">
-        <v>-1.14415817760739</v>
+        <v>1.716949596040392</v>
       </c>
       <c r="T25">
-        <v>-1.02285752781691</v>
+        <v>2.247716469837891</v>
       </c>
     </row>
     <row r="26">
@@ -2790,41 +3277,47 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_BB</t>
         </is>
       </c>
       <c r="H26">
-        <v>1.01413155993839</v>
+        <v>-0.6882130015174528</v>
+      </c>
+      <c r="I26">
+        <v>1.327063815072432</v>
+      </c>
+      <c r="J26">
+        <v>0.02476917652404654</v>
       </c>
       <c r="K26">
-        <v>1.01413155993839</v>
+        <v>-0.7702038729864665</v>
       </c>
       <c r="L26">
-        <v>0.132900404782863</v>
+        <v>-3.107214292744872</v>
       </c>
       <c r="M26">
-        <v>0.271945605126318</v>
+        <v>-2.697527175911463</v>
       </c>
       <c r="N26">
-        <v>0.421471846975689</v>
+        <v>-2.240661308673004</v>
       </c>
       <c r="O26">
-        <v>0.702677718412927</v>
+        <v>-1.518850158866036</v>
       </c>
       <c r="P26">
-        <v>1.01413155993839</v>
+        <v>-0.7702038729864665</v>
       </c>
       <c r="Q26">
-        <v>1.30765743401912</v>
+        <v>-0.05904362354368731</v>
       </c>
       <c r="R26">
-        <v>1.62045341082267</v>
+        <v>1.109443595377192</v>
       </c>
       <c r="S26">
-        <v>1.76983604142117</v>
+        <v>1.810098799883983</v>
       </c>
       <c r="T26">
-        <v>1.90879541650357</v>
+        <v>2.372299713557679</v>
       </c>
     </row>
     <row r="27">
@@ -2854,169 +3347,187 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H27">
-        <v>-0.495414542564131</v>
+        <v>0.6078452414098873</v>
+      </c>
+      <c r="I27">
+        <v>0.8864471303677438</v>
+      </c>
+      <c r="J27">
+        <v>0.0289047566794842</v>
       </c>
       <c r="K27">
-        <v>-0.495414542564131</v>
+        <v>0.7653375111660087</v>
       </c>
       <c r="L27">
-        <v>-1.52362447306495</v>
+        <v>-1.964062183754407</v>
       </c>
       <c r="M27">
-        <v>-1.35148821329627</v>
+        <v>-1.210673644941546</v>
       </c>
       <c r="N27">
-        <v>-1.1499129184622</v>
+        <v>-0.3246582539694939</v>
       </c>
       <c r="O27">
-        <v>-0.840610206815118</v>
+        <v>0.4213195500666771</v>
       </c>
       <c r="P27">
-        <v>-0.495414542564131</v>
+        <v>0.7653375111660087</v>
       </c>
       <c r="Q27">
-        <v>-0.125089258009898</v>
+        <v>1.046327088889025</v>
       </c>
       <c r="R27">
-        <v>0.159536350908174</v>
+        <v>1.322294322080186</v>
       </c>
       <c r="S27">
-        <v>0.31770835673824</v>
+        <v>1.551629891125228</v>
       </c>
       <c r="T27">
-        <v>0.436517430999924</v>
+        <v>1.840835948911052</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gaur</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DE</t>
+          <t>elev + slope</t>
         </is>
       </c>
       <c r="E28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>0.296</v>
+        <v>0.208</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>beta_BB</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H28">
-        <v>-0.994737806540444</v>
+        <v>-0.0544196745399779</v>
+      </c>
+      <c r="I28">
+        <v>1.294775909300191</v>
+      </c>
+      <c r="J28">
+        <v>0.01789030466328016</v>
       </c>
       <c r="K28">
-        <v>-0.994737806540444</v>
+        <v>-0.1638780530671466</v>
       </c>
       <c r="L28">
-        <v>-3.11308461045173</v>
+        <v>-2.750483851184881</v>
       </c>
       <c r="M28">
-        <v>-2.71268071408547</v>
+        <v>-2.249706084120765</v>
       </c>
       <c r="N28">
-        <v>-2.29658945325533</v>
+        <v>-1.649595864376685</v>
       </c>
       <c r="O28">
-        <v>-1.64161849070535</v>
+        <v>-0.6608675032378253</v>
       </c>
       <c r="P28">
-        <v>-0.994737806540444</v>
+        <v>-0.1638780530671466</v>
       </c>
       <c r="Q28">
-        <v>-0.491034043491208</v>
+        <v>0.6098915818924954</v>
       </c>
       <c r="R28">
-        <v>-0.176470337211962</v>
+        <v>1.652039356129778</v>
       </c>
       <c r="S28">
-        <v>-0.0165683824464211</v>
+        <v>2.306381313737713</v>
       </c>
       <c r="T28">
-        <v>0.117959738747891</v>
+        <v>2.807212147136925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gaur</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DE</t>
+          <t>elev + slope</t>
         </is>
       </c>
       <c r="E29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0.296</v>
+        <v>0.208</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>beta_DE</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H29">
-        <v>0.98589967797526</v>
+        <v>-0.4620453404196815</v>
+      </c>
+      <c r="I29">
+        <v>0.2545835225975315</v>
+      </c>
+      <c r="J29">
+        <v>0.01902824749432508</v>
       </c>
       <c r="K29">
-        <v>0.98589967797526</v>
+        <v>-0.4627417766160928</v>
       </c>
       <c r="L29">
-        <v>0.221613566732788</v>
+        <v>-0.7303429406133702</v>
       </c>
       <c r="M29">
-        <v>0.338495997281448</v>
+        <v>-0.6794998755070428</v>
       </c>
       <c r="N29">
-        <v>0.507922104059593</v>
+        <v>-0.6261253583693585</v>
       </c>
       <c r="O29">
-        <v>0.739916958861019</v>
+        <v>-0.5457208057008913</v>
       </c>
       <c r="P29">
-        <v>0.98589967797526</v>
+        <v>-0.4627417766160928</v>
       </c>
       <c r="Q29">
-        <v>1.23545753454557</v>
+        <v>-0.3857074056069053</v>
       </c>
       <c r="R29">
-        <v>1.45641958361124</v>
+        <v>-0.317289265376509</v>
       </c>
       <c r="S29">
-        <v>1.61041658025457</v>
+        <v>-0.2765012150572836</v>
       </c>
       <c r="T29">
-        <v>1.72944319952983</v>
+        <v>-0.2328814161841863</v>
       </c>
     </row>
     <row r="30">
@@ -3026,61 +3537,67 @@
         </is>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>slope</t>
         </is>
       </c>
       <c r="E30">
-        <v>1.78</v>
+        <v>0.23</v>
       </c>
       <c r="F30">
-        <v>0.08599999999999999</v>
+        <v>0.186</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H30">
-        <v>1.07405140668518</v>
+        <v>-0.4641479442825229</v>
+      </c>
+      <c r="I30">
+        <v>0.1337914400970451</v>
+      </c>
+      <c r="J30">
+        <v>0.005083105677329323</v>
       </c>
       <c r="K30">
-        <v>1.07405140668518</v>
+        <v>-0.4629818712561807</v>
       </c>
       <c r="L30">
-        <v>0.817777021540115</v>
+        <v>-0.7050612794147431</v>
       </c>
       <c r="M30">
-        <v>0.853175454069559</v>
+        <v>-0.663116549172501</v>
       </c>
       <c r="N30">
-        <v>0.897540703585668</v>
+        <v>-0.6183649119162893</v>
       </c>
       <c r="O30">
-        <v>0.982225773153378</v>
+        <v>-0.5440656514672902</v>
       </c>
       <c r="P30">
-        <v>1.07405140668518</v>
+        <v>-0.4629818712561807</v>
       </c>
       <c r="Q30">
-        <v>1.16817957659875</v>
+        <v>-0.3813302073263657</v>
       </c>
       <c r="R30">
-        <v>1.2497282163627</v>
+        <v>-0.3071454703408011</v>
       </c>
       <c r="S30">
-        <v>1.30594839748726</v>
+        <v>-0.2576345069383791</v>
       </c>
       <c r="T30">
-        <v>1.35309242714172</v>
+        <v>-0.219037243406177</v>
       </c>
     </row>
     <row r="31">
@@ -3090,61 +3607,67 @@
         </is>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>dist_str + elev + slope</t>
         </is>
       </c>
       <c r="E31">
-        <v>1.78</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
-        <v>0.08599999999999999</v>
+        <v>0.162</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>beta_slope</t>
+          <t>beta_dist_str</t>
         </is>
       </c>
       <c r="H31">
-        <v>-0.378595736814313</v>
+        <v>0.04231658722215414</v>
+      </c>
+      <c r="I31">
+        <v>1.39416752281747</v>
+      </c>
+      <c r="J31">
+        <v>0.01760588539611647</v>
       </c>
       <c r="K31">
-        <v>-0.378595736814313</v>
+        <v>0.102370817306454</v>
       </c>
       <c r="L31">
-        <v>-0.644264936586549</v>
+        <v>-2.769083381781887</v>
       </c>
       <c r="M31">
-        <v>-0.60699754266673</v>
+        <v>-2.34148459770346</v>
       </c>
       <c r="N31">
-        <v>-0.5572711229510811</v>
+        <v>-1.754833328554603</v>
       </c>
       <c r="O31">
-        <v>-0.469002699946436</v>
+        <v>-0.8236609665773931</v>
       </c>
       <c r="P31">
-        <v>-0.378595736814313</v>
+        <v>0.102370817306454</v>
       </c>
       <c r="Q31">
-        <v>-0.276341834639719</v>
+        <v>0.8456913509998593</v>
       </c>
       <c r="R31">
-        <v>-0.192872504107463</v>
+        <v>1.831407471918897</v>
       </c>
       <c r="S31">
-        <v>-0.139376447847833</v>
+        <v>2.369498202926786</v>
       </c>
       <c r="T31">
-        <v>-0.0942828409714854</v>
+        <v>2.880130954478207</v>
       </c>
     </row>
     <row r="32">
@@ -3154,151 +3677,163 @@
         </is>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>dist_str + elev + slope</t>
         </is>
       </c>
       <c r="E32">
-        <v>1.78</v>
+        <v>0.5</v>
       </c>
       <c r="F32">
-        <v>0.08599999999999999</v>
+        <v>0.162</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>beta_DE</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H32">
-        <v>-0.177221471563296</v>
+        <v>-0.05322354799165274</v>
+      </c>
+      <c r="I32">
+        <v>1.259278167990383</v>
+      </c>
+      <c r="J32">
+        <v>0.0184648995965419</v>
       </c>
       <c r="K32">
-        <v>-0.177221471563296</v>
+        <v>-0.1905124957029205</v>
       </c>
       <c r="L32">
-        <v>-0.49692814622282</v>
+        <v>-2.63108652468539</v>
       </c>
       <c r="M32">
-        <v>-0.435774592429638</v>
+        <v>-2.144392360643442</v>
       </c>
       <c r="N32">
-        <v>-0.380767144712005</v>
+        <v>-1.547796984145929</v>
       </c>
       <c r="O32">
-        <v>-0.28293251345545</v>
+        <v>-0.5571034844798201</v>
       </c>
       <c r="P32">
-        <v>-0.177221471563296</v>
+        <v>-0.1905124957029205</v>
       </c>
       <c r="Q32">
-        <v>-0.0845198490070406</v>
+        <v>0.5692175374369921</v>
       </c>
       <c r="R32">
-        <v>-0.00852748603690923</v>
+        <v>1.61907388982158</v>
       </c>
       <c r="S32">
-        <v>0.0339845847206532</v>
+        <v>2.237659017169348</v>
       </c>
       <c r="T32">
-        <v>0.0750051337890095</v>
+        <v>2.710765486804414</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + elev + slope</t>
         </is>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>0.399</v>
+        <v>0.162</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H33">
-        <v>-1.09167266865871</v>
+        <v>-0.4821605191000704</v>
+      </c>
+      <c r="I33">
+        <v>0.2115816286257022</v>
+      </c>
+      <c r="J33">
+        <v>0.01863794156541684</v>
       </c>
       <c r="K33">
-        <v>-1.09167266865871</v>
+        <v>-0.4672864559772039</v>
       </c>
       <c r="L33">
-        <v>-1.81910917878443</v>
+        <v>-0.7297814701663312</v>
       </c>
       <c r="M33">
-        <v>-1.70354713493108</v>
+        <v>-0.6783163678221694</v>
       </c>
       <c r="N33">
-        <v>-1.54818264596463</v>
+        <v>-0.6302464282499047</v>
       </c>
       <c r="O33">
-        <v>-1.33755752736795</v>
+        <v>-0.5519244356055517</v>
       </c>
       <c r="P33">
-        <v>-1.09167266865871</v>
+        <v>-0.4672864559772039</v>
       </c>
       <c r="Q33">
-        <v>-0.849687775154425</v>
+        <v>-0.3833053496120783</v>
       </c>
       <c r="R33">
-        <v>-0.624431270945473</v>
+        <v>-0.3124795855062717</v>
       </c>
       <c r="S33">
-        <v>-0.497658747917406</v>
+        <v>-0.2654350662298706</v>
       </c>
       <c r="T33">
-        <v>-0.383243888804548</v>
+        <v>-0.2307745050005367</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + elev + slope + BB</t>
         </is>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="F34">
-        <v>0.399</v>
+        <v>0.138</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3306,191 +3841,209 @@
         </is>
       </c>
       <c r="H34">
-        <v>0.0383486757232204</v>
+        <v>0.01036914889033713</v>
+      </c>
+      <c r="I34">
+        <v>1.404564076109158</v>
+      </c>
+      <c r="J34">
+        <v>0.01788740999307633</v>
       </c>
       <c r="K34">
-        <v>0.0383486757232204</v>
+        <v>0.05167792715745883</v>
       </c>
       <c r="L34">
-        <v>-0.605589256817529</v>
+        <v>-2.815494712852236</v>
       </c>
       <c r="M34">
-        <v>-0.479547144435942</v>
+        <v>-2.333132680200571</v>
       </c>
       <c r="N34">
-        <v>-0.362855458173382</v>
+        <v>-1.82715654949084</v>
       </c>
       <c r="O34">
-        <v>-0.164258778801576</v>
+        <v>-0.8725261599598371</v>
       </c>
       <c r="P34">
-        <v>0.0383486757232204</v>
+        <v>0.05167792715745883</v>
       </c>
       <c r="Q34">
-        <v>0.24985097619763</v>
+        <v>0.836432384344674</v>
       </c>
       <c r="R34">
-        <v>0.449145511837017</v>
+        <v>1.830998066756566</v>
       </c>
       <c r="S34">
-        <v>0.558891168197361</v>
+        <v>2.395247074261397</v>
       </c>
       <c r="T34">
-        <v>0.655691094910271</v>
+        <v>2.875526487378172</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + elev + slope + BB</t>
         </is>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="F35">
-        <v>0.399</v>
+        <v>0.138</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H35">
-        <v>-1.13091338627302</v>
+        <v>-0.06732394061969775</v>
+      </c>
+      <c r="I35">
+        <v>1.319123215964547</v>
+      </c>
+      <c r="J35">
+        <v>0.018293203543272</v>
       </c>
       <c r="K35">
-        <v>-1.13091338627302</v>
+        <v>-0.1704197531677483</v>
       </c>
       <c r="L35">
-        <v>-1.80071408294041</v>
+        <v>-2.809016821762637</v>
       </c>
       <c r="M35">
-        <v>-1.70104439990101</v>
+        <v>-2.344945128023159</v>
       </c>
       <c r="N35">
-        <v>-1.59470414093948</v>
+        <v>-1.734269326128276</v>
       </c>
       <c r="O35">
-        <v>-1.3728432692903</v>
+        <v>-0.6259941389785069</v>
       </c>
       <c r="P35">
-        <v>-1.13091338627302</v>
+        <v>-0.1704197531677483</v>
       </c>
       <c r="Q35">
-        <v>-0.935385829781613</v>
+        <v>0.6259215133103209</v>
       </c>
       <c r="R35">
-        <v>-0.753448891671335</v>
+        <v>1.669597923412479</v>
       </c>
       <c r="S35">
-        <v>-0.637918343032296</v>
+        <v>2.285179149496728</v>
       </c>
       <c r="T35">
-        <v>-0.52948118187852</v>
+        <v>2.759980584962631</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + elev + slope + BB</t>
         </is>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="F36">
-        <v>0.399</v>
+        <v>0.138</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H36">
-        <v>-2.36555332023772</v>
+        <v>-0.4794750317583447</v>
+      </c>
+      <c r="I36">
+        <v>0.1425818452388743</v>
+      </c>
+      <c r="J36">
+        <v>0.007280694400393682</v>
       </c>
       <c r="K36">
-        <v>-2.36555332023772</v>
+        <v>-0.4752907247058064</v>
       </c>
       <c r="L36">
-        <v>-3.08409709344872</v>
+        <v>-0.7351348770784424</v>
       </c>
       <c r="M36">
-        <v>-2.98600521570151</v>
+        <v>-0.6798829815533174</v>
       </c>
       <c r="N36">
-        <v>-2.87076003583092</v>
+        <v>-0.6341310951075825</v>
       </c>
       <c r="O36">
-        <v>-2.64612271540245</v>
+        <v>-0.5559341318978385</v>
       </c>
       <c r="P36">
-        <v>-2.36555332023772</v>
+        <v>-0.4752907247058064</v>
       </c>
       <c r="Q36">
-        <v>-2.09301955461122</v>
+        <v>-0.3917355366253205</v>
       </c>
       <c r="R36">
-        <v>-1.86205152724641</v>
+        <v>-0.3194652903651372</v>
       </c>
       <c r="S36">
-        <v>-1.68597235582323</v>
+        <v>-0.2738857140979759</v>
       </c>
       <c r="T36">
-        <v>-1.5512985289048</v>
+        <v>-0.2344341702019433</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + elev + slope + BB</t>
         </is>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="F37">
-        <v>0.399</v>
+        <v>0.138</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3498,191 +4051,209 @@
         </is>
       </c>
       <c r="H37">
-        <v>-1.33250538428134</v>
+        <v>-0.05088454988882122</v>
+      </c>
+      <c r="I37">
+        <v>1.386112592448698</v>
+      </c>
+      <c r="J37">
+        <v>0.02214943011304592</v>
       </c>
       <c r="K37">
-        <v>-1.33250538428134</v>
+        <v>0.02542884579505045</v>
       </c>
       <c r="L37">
-        <v>-3.52159165659489</v>
+        <v>-2.858297110022291</v>
       </c>
       <c r="M37">
-        <v>-3.10176596914126</v>
+        <v>-2.353512228550074</v>
       </c>
       <c r="N37">
-        <v>-2.64507377355787</v>
+        <v>-1.814557209520452</v>
       </c>
       <c r="O37">
-        <v>-1.98656705841723</v>
+        <v>-0.9128631067214185</v>
       </c>
       <c r="P37">
-        <v>-1.33250538428134</v>
+        <v>0.02542884579505045</v>
       </c>
       <c r="Q37">
-        <v>-0.761155302700917</v>
+        <v>0.7249835385328802</v>
       </c>
       <c r="R37">
-        <v>-0.316917482082253</v>
+        <v>1.719230289369014</v>
       </c>
       <c r="S37">
-        <v>-0.105762141666758</v>
+        <v>2.33617741645584</v>
       </c>
       <c r="T37">
-        <v>0.041226650217689</v>
+        <v>2.81406876044557</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+          <t>slope + DE</t>
         </is>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F38">
-        <v>0.399</v>
+        <v>0.13</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>beta_DD</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H38">
-        <v>-0.48332502924255</v>
+        <v>-0.4615748200550503</v>
+      </c>
+      <c r="I38">
+        <v>0.1261112536780309</v>
+      </c>
+      <c r="J38">
+        <v>0.004299103327344304</v>
       </c>
       <c r="K38">
-        <v>-0.48332502924255</v>
+        <v>-0.4634950397947061</v>
       </c>
       <c r="L38">
-        <v>-1.88251285338097</v>
+        <v>-0.7096801342698165</v>
       </c>
       <c r="M38">
-        <v>-1.57869205452822</v>
+        <v>-0.666361111563525</v>
       </c>
       <c r="N38">
-        <v>-1.28717378662065</v>
+        <v>-0.6204298367069817</v>
       </c>
       <c r="O38">
-        <v>-0.875138998281031</v>
+        <v>-0.5461778340707911</v>
       </c>
       <c r="P38">
-        <v>-0.48332502924255</v>
+        <v>-0.4634950397947061</v>
       </c>
       <c r="Q38">
-        <v>-0.212050341449445</v>
+        <v>-0.3785126758118824</v>
       </c>
       <c r="R38">
-        <v>0.009144392998675741</v>
+        <v>-0.3015444885870587</v>
       </c>
       <c r="S38">
-        <v>0.116518615320811</v>
+        <v>-0.2573942806043321</v>
       </c>
       <c r="T38">
-        <v>0.207180904763053</v>
+        <v>-0.2174152981839113</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB</t>
+          <t>slope + DE</t>
         </is>
       </c>
       <c r="E39">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F39">
-        <v>0.248</v>
+        <v>0.13</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H39">
-        <v>-0.8540081936545471</v>
+        <v>-0.06094676626529596</v>
+      </c>
+      <c r="I39">
+        <v>1.356230679171389</v>
+      </c>
+      <c r="J39">
+        <v>0.01734071867631386</v>
       </c>
       <c r="K39">
-        <v>-0.8540081936545471</v>
+        <v>-0.1526651941773805</v>
       </c>
       <c r="L39">
-        <v>-1.51347226325948</v>
+        <v>-2.824951133313192</v>
       </c>
       <c r="M39">
-        <v>-1.42738640250991</v>
+        <v>-2.335341195508677</v>
       </c>
       <c r="N39">
-        <v>-1.30718251841308</v>
+        <v>-1.773776177152041</v>
       </c>
       <c r="O39">
-        <v>-1.09077646111523</v>
+        <v>-0.7699343532481444</v>
       </c>
       <c r="P39">
-        <v>-0.8540081936545471</v>
+        <v>-0.1526651941773805</v>
       </c>
       <c r="Q39">
-        <v>-0.634244442608356</v>
+        <v>0.7131014793856458</v>
       </c>
       <c r="R39">
-        <v>-0.44608111243012</v>
+        <v>1.725629829064253</v>
       </c>
       <c r="S39">
-        <v>-0.329303540792073</v>
+        <v>2.3121396561706</v>
       </c>
       <c r="T39">
-        <v>-0.235589287348351</v>
+        <v>2.772906406515366</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB</t>
+          <t>ndvi_cv + slope</t>
         </is>
       </c>
       <c r="E40">
-        <v>0.95</v>
+        <v>1.67</v>
       </c>
       <c r="F40">
-        <v>0.248</v>
+        <v>0.09</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3690,111 +4261,123 @@
         </is>
       </c>
       <c r="H40">
-        <v>-1.26330521503005</v>
+        <v>-0.01487893447078034</v>
+      </c>
+      <c r="I40">
+        <v>1.449613695752614</v>
+      </c>
+      <c r="J40">
+        <v>0.01798237034759213</v>
       </c>
       <c r="K40">
-        <v>-1.26330521503005</v>
+        <v>0.02707702394709099</v>
       </c>
       <c r="L40">
-        <v>-1.78171494226729</v>
+        <v>-2.860761058557257</v>
       </c>
       <c r="M40">
-        <v>-1.70578289831481</v>
+        <v>-2.39267422575917</v>
       </c>
       <c r="N40">
-        <v>-1.61401260953999</v>
+        <v>-1.883528414755468</v>
       </c>
       <c r="O40">
-        <v>-1.45948188364552</v>
+        <v>-0.9476020842083177</v>
       </c>
       <c r="P40">
-        <v>-1.26330521503005</v>
+        <v>0.02707702394709099</v>
       </c>
       <c r="Q40">
-        <v>-1.06003488174625</v>
+        <v>0.8968350919693733</v>
       </c>
       <c r="R40">
-        <v>-0.886918143414686</v>
+        <v>1.873946747209562</v>
       </c>
       <c r="S40">
-        <v>-0.796820610141294</v>
+        <v>2.422589707661751</v>
       </c>
       <c r="T40">
-        <v>-0.7057987699471751</v>
+        <v>2.89169479362201</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB</t>
+          <t>ndvi_cv + slope</t>
         </is>
       </c>
       <c r="E41">
-        <v>0.95</v>
+        <v>1.67</v>
       </c>
       <c r="F41">
-        <v>0.248</v>
+        <v>0.09</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H41">
-        <v>-2.34237891611451</v>
+        <v>-0.4703080365246954</v>
+      </c>
+      <c r="I41">
+        <v>0.1192603201601333</v>
+      </c>
+      <c r="J41">
+        <v>0.003902463066487625</v>
       </c>
       <c r="K41">
-        <v>-2.34237891611451</v>
+        <v>-0.469194189098487</v>
       </c>
       <c r="L41">
-        <v>-2.87413301958752</v>
+        <v>-0.7003034279930308</v>
       </c>
       <c r="M41">
-        <v>-2.7885313052878</v>
+        <v>-0.6652088579201505</v>
       </c>
       <c r="N41">
-        <v>-2.69921052975566</v>
+        <v>-0.6227351157980305</v>
       </c>
       <c r="O41">
-        <v>-2.53029447273778</v>
+        <v>-0.5515770752424153</v>
       </c>
       <c r="P41">
-        <v>-2.34237891611451</v>
+        <v>-0.469194189098487</v>
       </c>
       <c r="Q41">
-        <v>-2.14821170117781</v>
+        <v>-0.3902228094884012</v>
       </c>
       <c r="R41">
-        <v>-1.98460043599753</v>
+        <v>-0.3187429664989092</v>
       </c>
       <c r="S41">
-        <v>-1.88665661375306</v>
+        <v>-0.277403969123182</v>
       </c>
       <c r="T41">
-        <v>-1.77011861743285</v>
+        <v>-0.2393618681648919</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -3803,62 +4386,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB</t>
+          <t>slope + DE</t>
         </is>
       </c>
       <c r="E42">
-        <v>0.95</v>
+        <v>1.78</v>
       </c>
       <c r="F42">
-        <v>0.248</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>beta_BB</t>
+          <t>beta0 (Intercept)</t>
         </is>
       </c>
       <c r="H42">
-        <v>-1.42936862427318</v>
+        <v>0.9913246815817253</v>
+      </c>
+      <c r="I42">
+        <v>0.1486425865056107</v>
+      </c>
+      <c r="J42">
+        <v>0.07213722008225137</v>
       </c>
       <c r="K42">
-        <v>-1.42936862427318</v>
+        <v>0.9878755523844958</v>
       </c>
       <c r="L42">
-        <v>-3.37361234570619</v>
+        <v>0.7279944877166254</v>
       </c>
       <c r="M42">
-        <v>-3.01189216714425</v>
+        <v>0.7371188449482147</v>
       </c>
       <c r="N42">
-        <v>-2.69636197596794</v>
+        <v>0.7743181150038695</v>
       </c>
       <c r="O42">
-        <v>-2.10789862175422</v>
+        <v>0.8619205289881153</v>
       </c>
       <c r="P42">
-        <v>-1.42936862427318</v>
+        <v>0.9878755523844958</v>
       </c>
       <c r="Q42">
-        <v>-0.872494575029033</v>
+        <v>1.117927317454629</v>
       </c>
       <c r="R42">
-        <v>-0.448601518037732</v>
+        <v>1.16541726466529</v>
       </c>
       <c r="S42">
-        <v>-0.209594269697237</v>
+        <v>1.187348662974869</v>
       </c>
       <c r="T42">
-        <v>-0.0405360362422776</v>
+        <v>1.238820953748188</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3867,62 +4456,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DD</t>
+          <t>slope + DE</t>
         </is>
       </c>
       <c r="E43">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="F43">
-        <v>0.188</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_slope</t>
         </is>
       </c>
       <c r="H43">
-        <v>-1.02018854438725</v>
+        <v>-0.3838608964561235</v>
+      </c>
+      <c r="I43">
+        <v>0.1465721466766946</v>
+      </c>
+      <c r="J43">
+        <v>0.05303669350570862</v>
       </c>
       <c r="K43">
-        <v>-1.02018854438725</v>
+        <v>-0.3832811766334352</v>
       </c>
       <c r="L43">
-        <v>-1.80728672852912</v>
+        <v>-0.6370263417604732</v>
       </c>
       <c r="M43">
-        <v>-1.6557400582839</v>
+        <v>-0.6352017157346311</v>
       </c>
       <c r="N43">
-        <v>-1.4952674321361</v>
+        <v>-0.5991325373380201</v>
       </c>
       <c r="O43">
-        <v>-1.26020248957157</v>
+        <v>-0.4907754903044245</v>
       </c>
       <c r="P43">
-        <v>-1.02018854438725</v>
+        <v>-0.3832811766334352</v>
       </c>
       <c r="Q43">
-        <v>-0.796169084647451</v>
+        <v>-0.2714155725936253</v>
       </c>
       <c r="R43">
-        <v>-0.593037921766594</v>
+        <v>-0.1890848368035216</v>
       </c>
       <c r="S43">
-        <v>-0.471489095434699</v>
+        <v>-0.1761133258253265</v>
       </c>
       <c r="T43">
-        <v>-0.363277510744215</v>
+        <v>-0.1587382419982914</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sambar deer</t>
+          <t>Muntjac</t>
         </is>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3931,52 +4526,58 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DD</t>
+          <t>slope + DE</t>
         </is>
       </c>
       <c r="E44">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="F44">
-        <v>0.188</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H44">
-        <v>-1.22010381494236</v>
+        <v>-0.1931206743608491</v>
+      </c>
+      <c r="I44">
+        <v>0.09717644539779957</v>
+      </c>
+      <c r="J44">
+        <v>0.01264439576963174</v>
       </c>
       <c r="K44">
-        <v>-1.22010381494236</v>
+        <v>-0.1910095792674409</v>
       </c>
       <c r="L44">
-        <v>-1.80476614581316</v>
+        <v>-0.3750590435853822</v>
       </c>
       <c r="M44">
-        <v>-1.72227014646008</v>
+        <v>-0.3393807437646424</v>
       </c>
       <c r="N44">
-        <v>-1.60936725369676</v>
+        <v>-0.3181927035743626</v>
       </c>
       <c r="O44">
-        <v>-1.42737156436513</v>
+        <v>-0.2616662465359703</v>
       </c>
       <c r="P44">
-        <v>-1.22010381494236</v>
+        <v>-0.1910095792674409</v>
       </c>
       <c r="Q44">
-        <v>-1.0214572073894</v>
+        <v>-0.1203834756936969</v>
       </c>
       <c r="R44">
-        <v>-0.843212934590748</v>
+        <v>-0.0748755040922944</v>
       </c>
       <c r="S44">
-        <v>-0.724676576738432</v>
+        <v>-0.03198693983440308</v>
       </c>
       <c r="T44">
-        <v>-0.614861237544844</v>
+        <v>-0.01161898846837328</v>
       </c>
     </row>
     <row r="45">
@@ -3986,7 +4587,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3995,52 +4596,58 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
         </is>
       </c>
       <c r="E45">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0.188</v>
+        <v>0.399</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta0 (Intercept)</t>
         </is>
       </c>
       <c r="H45">
-        <v>-2.21560202854327</v>
+        <v>-0.8343754707424136</v>
+      </c>
+      <c r="I45">
+        <v>0.2848731536250926</v>
+      </c>
+      <c r="J45">
+        <v>0.1318117273209451</v>
       </c>
       <c r="K45">
-        <v>-2.21560202854327</v>
+        <v>-0.834971772416631</v>
       </c>
       <c r="L45">
-        <v>-2.91103249588617</v>
+        <v>-1.272171912047676</v>
       </c>
       <c r="M45">
-        <v>-2.80631746499368</v>
+        <v>-1.243040391847961</v>
       </c>
       <c r="N45">
-        <v>-2.66667039908178</v>
+        <v>-1.208698155799748</v>
       </c>
       <c r="O45">
-        <v>-2.44369159131239</v>
+        <v>-1.052457822131593</v>
       </c>
       <c r="P45">
-        <v>-2.21560202854327</v>
+        <v>-0.834971772416631</v>
       </c>
       <c r="Q45">
-        <v>-2.03286610009253</v>
+        <v>-0.5835761419880313</v>
       </c>
       <c r="R45">
-        <v>-1.85973588321558</v>
+        <v>-0.4481062700124688</v>
       </c>
       <c r="S45">
-        <v>-1.73804266214156</v>
+        <v>-0.426372315667659</v>
       </c>
       <c r="T45">
-        <v>-1.63365409182055</v>
+        <v>-0.3712083330414118</v>
       </c>
     </row>
     <row r="46">
@@ -4050,7 +4657,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -4059,52 +4666,58 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + BB + DD</t>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
         </is>
       </c>
       <c r="E46">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>0.188</v>
+        <v>0.399</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>beta_BB</t>
+          <t>beta_dist_str</t>
         </is>
       </c>
       <c r="H46">
-        <v>-1.72176479188108</v>
+        <v>0.1666347000990206</v>
+      </c>
+      <c r="I46">
+        <v>0.2216982370608659</v>
+      </c>
+      <c r="J46">
+        <v>0.07268657435264894</v>
       </c>
       <c r="K46">
-        <v>-1.72176479188108</v>
+        <v>0.1343873165366745</v>
       </c>
       <c r="L46">
-        <v>-4.33356582005306</v>
+        <v>-0.2524574607495085</v>
       </c>
       <c r="M46">
-        <v>-3.73466299556028</v>
+        <v>-0.1340495786478707</v>
       </c>
       <c r="N46">
-        <v>-3.21355098928141</v>
+        <v>-0.08954350469411443</v>
       </c>
       <c r="O46">
-        <v>-2.48717880799542</v>
+        <v>0.02352968132968275</v>
       </c>
       <c r="P46">
-        <v>-1.72176479188108</v>
+        <v>0.1343873165366745</v>
       </c>
       <c r="Q46">
-        <v>-1.01918963184879</v>
+        <v>0.2922957698564618</v>
       </c>
       <c r="R46">
-        <v>-0.484894237710295</v>
+        <v>0.5113550234708423</v>
       </c>
       <c r="S46">
-        <v>-0.207075116931636</v>
+        <v>0.5591394586229723</v>
       </c>
       <c r="T46">
-        <v>-0.0682909392804618</v>
+        <v>0.6077455854179703</v>
       </c>
     </row>
     <row r="47">
@@ -4114,61 +4727,1257 @@
         </is>
       </c>
       <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0.399</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>beta_ndvi_cv</t>
+        </is>
+      </c>
+      <c r="H47">
+        <v>-1.152656882502407</v>
+      </c>
+      <c r="I47">
+        <v>0.1534220233378837</v>
+      </c>
+      <c r="J47">
+        <v>0.02667379745960026</v>
+      </c>
+      <c r="K47">
+        <v>-1.164409210368508</v>
+      </c>
+      <c r="L47">
+        <v>-1.531342575457185</v>
+      </c>
+      <c r="M47">
+        <v>-1.41036055968669</v>
+      </c>
+      <c r="N47">
+        <v>-1.34747180972</v>
+      </c>
+      <c r="O47">
+        <v>-1.224940057495803</v>
+      </c>
+      <c r="P47">
+        <v>-1.164409210368508</v>
+      </c>
+      <c r="Q47">
+        <v>-1.043609254764194</v>
+      </c>
+      <c r="R47">
+        <v>-0.9599176884694822</v>
+      </c>
+      <c r="S47">
+        <v>-0.9144199906028663</v>
+      </c>
+      <c r="T47">
+        <v>-0.9008671911962983</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0.399</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>beta_elev</t>
+        </is>
+      </c>
+      <c r="H48">
+        <v>-2.211594343673157</v>
+      </c>
+      <c r="I48">
+        <v>0.2230004440914079</v>
+      </c>
+      <c r="J48">
+        <v>0.1055656189432634</v>
+      </c>
+      <c r="K48">
+        <v>-2.261254392023111</v>
+      </c>
+      <c r="L48">
+        <v>-2.631169242103466</v>
+      </c>
+      <c r="M48">
+        <v>-2.574233158527166</v>
+      </c>
+      <c r="N48">
+        <v>-2.478442942875799</v>
+      </c>
+      <c r="O48">
+        <v>-2.379584904008128</v>
+      </c>
+      <c r="P48">
+        <v>-2.261254392023111</v>
+      </c>
+      <c r="Q48">
+        <v>-2.065333990778402</v>
+      </c>
+      <c r="R48">
+        <v>-1.860650147893161</v>
+      </c>
+      <c r="S48">
+        <v>-1.783263279018806</v>
+      </c>
+      <c r="T48">
+        <v>-1.769872645678602</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0.399</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H49">
+        <v>-2.097587353880819</v>
+      </c>
+      <c r="I49">
+        <v>0.8651976283011569</v>
+      </c>
+      <c r="J49">
+        <v>0.2518497575176931</v>
+      </c>
+      <c r="K49">
+        <v>-2.021166403046479</v>
+      </c>
+      <c r="L49">
+        <v>-3.89025328560212</v>
+      </c>
+      <c r="M49">
+        <v>-3.641075236959403</v>
+      </c>
+      <c r="N49">
+        <v>-3.197472366120072</v>
+      </c>
+      <c r="O49">
+        <v>-2.827192751717598</v>
+      </c>
+      <c r="P49">
+        <v>-2.021166403046479</v>
+      </c>
+      <c r="Q49">
+        <v>-1.3729525806744</v>
+      </c>
+      <c r="R49">
+        <v>-0.9651058538183455</v>
+      </c>
+      <c r="S49">
+        <v>-0.884137529495442</v>
+      </c>
+      <c r="T49">
+        <v>-0.7262242602939739</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>dist_str + ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0.399</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>beta_DD</t>
+        </is>
+      </c>
+      <c r="H50">
+        <v>-0.5510156381020054</v>
+      </c>
+      <c r="I50">
+        <v>0.3290178164927073</v>
+      </c>
+      <c r="J50">
+        <v>0.05456015077725753</v>
+      </c>
+      <c r="K50">
+        <v>-0.5157394755421896</v>
+      </c>
+      <c r="L50">
+        <v>-1.272737071453193</v>
+      </c>
+      <c r="M50">
+        <v>-1.181335563467513</v>
+      </c>
+      <c r="N50">
+        <v>-0.957162199504825</v>
+      </c>
+      <c r="O50">
+        <v>-0.739647846328114</v>
+      </c>
+      <c r="P50">
+        <v>-0.5157394755421896</v>
+      </c>
+      <c r="Q50">
+        <v>-0.3572558492900185</v>
+      </c>
+      <c r="R50">
+        <v>-0.1185068443429195</v>
+      </c>
+      <c r="S50">
+        <v>-0.03209639160380096</v>
+      </c>
+      <c r="T50">
+        <v>0.02911554702556507</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB</t>
+        </is>
+      </c>
+      <c r="E51">
+        <v>0.95</v>
+      </c>
+      <c r="F51">
+        <v>0.248</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H51">
+        <v>-0.7307667586694649</v>
+      </c>
+      <c r="I51">
+        <v>0.2711093592647267</v>
+      </c>
+      <c r="J51">
+        <v>0.1344028879325774</v>
+      </c>
+      <c r="K51">
+        <v>-0.7123076567262183</v>
+      </c>
+      <c r="L51">
+        <v>-1.13625589975834</v>
+      </c>
+      <c r="M51">
+        <v>-1.10132975232478</v>
+      </c>
+      <c r="N51">
+        <v>-1.077469438244685</v>
+      </c>
+      <c r="O51">
+        <v>-0.9684247740413162</v>
+      </c>
+      <c r="P51">
+        <v>-0.7123076567262183</v>
+      </c>
+      <c r="Q51">
+        <v>-0.5269421038278028</v>
+      </c>
+      <c r="R51">
+        <v>-0.3206197185541889</v>
+      </c>
+      <c r="S51">
+        <v>-0.2190351026446799</v>
+      </c>
+      <c r="T51">
+        <v>-0.2190351026446799</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>0.95</v>
+      </c>
+      <c r="F52">
+        <v>0.248</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>beta_ndvi_cv</t>
+        </is>
+      </c>
+      <c r="H52">
+        <v>-1.177724120277592</v>
+      </c>
+      <c r="I52">
+        <v>0.1368646713877105</v>
+      </c>
+      <c r="J52">
+        <v>0.02481612889605708</v>
+      </c>
+      <c r="K52">
+        <v>-1.194016191431254</v>
+      </c>
+      <c r="L52">
+        <v>-1.395478038275788</v>
+      </c>
+      <c r="M52">
+        <v>-1.382069213708613</v>
+      </c>
+      <c r="N52">
+        <v>-1.352111583967158</v>
+      </c>
+      <c r="O52">
+        <v>-1.277066351409607</v>
+      </c>
+      <c r="P52">
+        <v>-1.194016191431254</v>
+      </c>
+      <c r="Q52">
+        <v>-1.088914660138022</v>
+      </c>
+      <c r="R52">
+        <v>-0.9682120362962292</v>
+      </c>
+      <c r="S52">
+        <v>-0.9441014632173645</v>
+      </c>
+      <c r="T52">
+        <v>-0.8822498673889991</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>0.95</v>
+      </c>
+      <c r="F53">
+        <v>0.248</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>beta_elev</t>
+        </is>
+      </c>
+      <c r="H53">
+        <v>-2.183381184170333</v>
+      </c>
+      <c r="I53">
+        <v>0.1707842885476979</v>
+      </c>
+      <c r="J53">
+        <v>0.06724572168354724</v>
+      </c>
+      <c r="K53">
+        <v>-2.19042616286217</v>
+      </c>
+      <c r="L53">
+        <v>-2.483612123412183</v>
+      </c>
+      <c r="M53">
+        <v>-2.483485409434572</v>
+      </c>
+      <c r="N53">
+        <v>-2.421520067693024</v>
+      </c>
+      <c r="O53">
+        <v>-2.285019101803254</v>
+      </c>
+      <c r="P53">
+        <v>-2.19042616286217</v>
+      </c>
+      <c r="Q53">
+        <v>-2.074715340740159</v>
+      </c>
+      <c r="R53">
+        <v>-1.899841240683838</v>
+      </c>
+      <c r="S53">
+        <v>-1.865669371039645</v>
+      </c>
+      <c r="T53">
+        <v>-1.865669371039645</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>0.95</v>
+      </c>
+      <c r="F54">
+        <v>0.248</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H54">
+        <v>-1.828658726768258</v>
+      </c>
+      <c r="I54">
+        <v>0.8207240677098363</v>
+      </c>
+      <c r="J54">
+        <v>0.2792716561825207</v>
+      </c>
+      <c r="K54">
+        <v>-1.63565078000148</v>
+      </c>
+      <c r="L54">
+        <v>-3.703724220311459</v>
+      </c>
+      <c r="M54">
+        <v>-3.47891583890407</v>
+      </c>
+      <c r="N54">
+        <v>-3.057503523505131</v>
+      </c>
+      <c r="O54">
+        <v>-2.362750045495978</v>
+      </c>
+      <c r="P54">
+        <v>-1.63565078000148</v>
+      </c>
+      <c r="Q54">
+        <v>-1.255605029209338</v>
+      </c>
+      <c r="R54">
+        <v>-0.8898094956368673</v>
+      </c>
+      <c r="S54">
+        <v>-0.6199082577582717</v>
+      </c>
+      <c r="T54">
+        <v>-0.5957311636908798</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B55">
         <v>3</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Spatial</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>ndvi_cv + elev + BB + DD</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E55">
         <v>1.5</v>
       </c>
-      <c r="F47">
+      <c r="F55">
         <v>0.188</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H55">
+        <v>-0.5411538283408674</v>
+      </c>
+      <c r="I55">
+        <v>0.1934066469517847</v>
+      </c>
+      <c r="J55">
+        <v>0.07114251696824865</v>
+      </c>
+      <c r="K55">
+        <v>-0.5498953132538859</v>
+      </c>
+      <c r="L55">
+        <v>-0.8241269743819788</v>
+      </c>
+      <c r="M55">
+        <v>-0.818189057612336</v>
+      </c>
+      <c r="N55">
+        <v>-0.7818787488197412</v>
+      </c>
+      <c r="O55">
+        <v>-0.7275035718906924</v>
+      </c>
+      <c r="P55">
+        <v>-0.5498953132538859</v>
+      </c>
+      <c r="Q55">
+        <v>-0.357563126834899</v>
+      </c>
+      <c r="R55">
+        <v>-0.2885659161026625</v>
+      </c>
+      <c r="S55">
+        <v>-0.2604523542345711</v>
+      </c>
+      <c r="T55">
+        <v>-0.2086753291202262</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>1.5</v>
+      </c>
+      <c r="F56">
+        <v>0.188</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>beta_ndvi_cv</t>
+        </is>
+      </c>
+      <c r="H56">
+        <v>-1.010819589280612</v>
+      </c>
+      <c r="I56">
+        <v>0.2251398323717008</v>
+      </c>
+      <c r="J56">
+        <v>0.06482858120536823</v>
+      </c>
+      <c r="K56">
+        <v>-1.035188141484134</v>
+      </c>
+      <c r="L56">
+        <v>-1.383410554548667</v>
+      </c>
+      <c r="M56">
+        <v>-1.314317961004864</v>
+      </c>
+      <c r="N56">
+        <v>-1.260350933013959</v>
+      </c>
+      <c r="O56">
+        <v>-1.181524690764977</v>
+      </c>
+      <c r="P56">
+        <v>-1.035188141484134</v>
+      </c>
+      <c r="Q56">
+        <v>-0.8905037791611714</v>
+      </c>
+      <c r="R56">
+        <v>-0.7788305210909211</v>
+      </c>
+      <c r="S56">
+        <v>-0.4798134021950344</v>
+      </c>
+      <c r="T56">
+        <v>-0.4563092624652844</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E57">
+        <v>1.5</v>
+      </c>
+      <c r="F57">
+        <v>0.188</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>beta_elev</t>
+        </is>
+      </c>
+      <c r="H57">
+        <v>-1.956175385055819</v>
+      </c>
+      <c r="I57">
+        <v>0.2579258938796519</v>
+      </c>
+      <c r="J57">
+        <v>0.1095358050906857</v>
+      </c>
+      <c r="K57">
+        <v>-2.048337711515549</v>
+      </c>
+      <c r="L57">
+        <v>-2.269812550053572</v>
+      </c>
+      <c r="M57">
+        <v>-2.263588028867993</v>
+      </c>
+      <c r="N57">
+        <v>-2.197305032928032</v>
+      </c>
+      <c r="O57">
+        <v>-2.141065974232298</v>
+      </c>
+      <c r="P57">
+        <v>-2.048337711515549</v>
+      </c>
+      <c r="Q57">
+        <v>-1.823437846127612</v>
+      </c>
+      <c r="R57">
+        <v>-1.659450972852719</v>
+      </c>
+      <c r="S57">
+        <v>-1.257892346222186</v>
+      </c>
+      <c r="T57">
+        <v>-1.191574795635222</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E58">
+        <v>1.5</v>
+      </c>
+      <c r="F58">
+        <v>0.188</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H58">
+        <v>-1.459230838703992</v>
+      </c>
+      <c r="I58">
+        <v>0.4777576664002882</v>
+      </c>
+      <c r="J58">
+        <v>0.08529618837960391</v>
+      </c>
+      <c r="K58">
+        <v>-1.366926788490725</v>
+      </c>
+      <c r="L58">
+        <v>-2.489786496817119</v>
+      </c>
+      <c r="M58">
+        <v>-2.298774975130094</v>
+      </c>
+      <c r="N58">
+        <v>-2.116852360211993</v>
+      </c>
+      <c r="O58">
+        <v>-1.793823604619208</v>
+      </c>
+      <c r="P58">
+        <v>-1.366926788490725</v>
+      </c>
+      <c r="Q58">
+        <v>-1.128836226710184</v>
+      </c>
+      <c r="R58">
+        <v>-0.885616211241669</v>
+      </c>
+      <c r="S58">
+        <v>-0.7368495039814162</v>
+      </c>
+      <c r="T58">
+        <v>-0.6658932631656005</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sambar deer</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ndvi_cv + elev + BB + DD</t>
+        </is>
+      </c>
+      <c r="E59">
+        <v>1.5</v>
+      </c>
+      <c r="F59">
+        <v>0.188</v>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>beta_DD</t>
         </is>
       </c>
-      <c r="H47">
-        <v>-0.580310053605375</v>
-      </c>
-      <c r="K47">
-        <v>-0.580310053605375</v>
-      </c>
-      <c r="L47">
-        <v>-2.1287663829272</v>
-      </c>
-      <c r="M47">
-        <v>-1.82030933512784</v>
-      </c>
-      <c r="N47">
-        <v>-1.49189950795506</v>
-      </c>
-      <c r="O47">
-        <v>-1.00269206829709</v>
-      </c>
-      <c r="P47">
-        <v>-0.580310053605375</v>
-      </c>
-      <c r="Q47">
-        <v>-0.256392796445441</v>
-      </c>
-      <c r="R47">
-        <v>-0.0285208587641077</v>
-      </c>
-      <c r="S47">
-        <v>0.09828884157455541</v>
-      </c>
-      <c r="T47">
-        <v>0.195668832424048</v>
+      <c r="H59">
+        <v>-0.4205532588851846</v>
+      </c>
+      <c r="I59">
+        <v>0.3085782102603682</v>
+      </c>
+      <c r="J59">
+        <v>0.05885893839320223</v>
+      </c>
+      <c r="K59">
+        <v>-0.3589789550319535</v>
+      </c>
+      <c r="L59">
+        <v>-1.37624127345034</v>
+      </c>
+      <c r="M59">
+        <v>-0.9284289663258757</v>
+      </c>
+      <c r="N59">
+        <v>-0.7475488337204534</v>
+      </c>
+      <c r="O59">
+        <v>-0.6012722334420149</v>
+      </c>
+      <c r="P59">
+        <v>-0.3589789550319535</v>
+      </c>
+      <c r="Q59">
+        <v>-0.2052124264072147</v>
+      </c>
+      <c r="R59">
+        <v>-0.1096284111204457</v>
+      </c>
+      <c r="S59">
+        <v>-0.05998842837792913</v>
+      </c>
+      <c r="T59">
+        <v>-0.02030566477183715</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0.527</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H60">
+        <v>0.05054202369146823</v>
+      </c>
+      <c r="I60">
+        <v>0.18293473449882</v>
+      </c>
+      <c r="J60">
+        <v>0.02973638249281557</v>
+      </c>
+      <c r="K60">
+        <v>0.06849731900321554</v>
+      </c>
+      <c r="L60">
+        <v>-0.3392071389383966</v>
+      </c>
+      <c r="M60">
+        <v>-0.3277277151963257</v>
+      </c>
+      <c r="N60">
+        <v>-0.1980056925305528</v>
+      </c>
+      <c r="O60">
+        <v>-0.06215808876269596</v>
+      </c>
+      <c r="P60">
+        <v>0.06849731900321554</v>
+      </c>
+      <c r="Q60">
+        <v>0.179236479877801</v>
+      </c>
+      <c r="R60">
+        <v>0.271673311941279</v>
+      </c>
+      <c r="S60">
+        <v>0.3404629553279683</v>
+      </c>
+      <c r="T60">
+        <v>0.3765036166037736</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0.527</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H61">
+        <v>0.4755651908038078</v>
+      </c>
+      <c r="I61">
+        <v>0.2002705337387587</v>
+      </c>
+      <c r="J61">
+        <v>0.0271018785245539</v>
+      </c>
+      <c r="K61">
+        <v>0.4995359809654409</v>
+      </c>
+      <c r="L61">
+        <v>0.09784859383797573</v>
+      </c>
+      <c r="M61">
+        <v>0.1110114021830484</v>
+      </c>
+      <c r="N61">
+        <v>0.1641154136389191</v>
+      </c>
+      <c r="O61">
+        <v>0.3494439742191254</v>
+      </c>
+      <c r="P61">
+        <v>0.4995359809654409</v>
+      </c>
+      <c r="Q61">
+        <v>0.6323846662815329</v>
+      </c>
+      <c r="R61">
+        <v>0.7170164003171264</v>
+      </c>
+      <c r="S61">
+        <v>0.7788188954757386</v>
+      </c>
+      <c r="T61">
+        <v>0.7976733698878778</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>slope + BB</t>
+        </is>
+      </c>
+      <c r="E62">
+        <v>0.68</v>
+      </c>
+      <c r="F62">
+        <v>0.375</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H62">
+        <v>-0.1700574849594609</v>
+      </c>
+      <c r="I62">
+        <v>0.236909529928073</v>
+      </c>
+      <c r="J62">
+        <v>0.0485347774459452</v>
+      </c>
+      <c r="K62">
+        <v>-0.1339026613417365</v>
+      </c>
+      <c r="L62">
+        <v>-0.589878074973992</v>
+      </c>
+      <c r="M62">
+        <v>-0.589878074973992</v>
+      </c>
+      <c r="N62">
+        <v>-0.5081418554541016</v>
+      </c>
+      <c r="O62">
+        <v>-0.3336773859602196</v>
+      </c>
+      <c r="P62">
+        <v>-0.1339026613417365</v>
+      </c>
+      <c r="Q62">
+        <v>-0.006045483630314619</v>
+      </c>
+      <c r="R62">
+        <v>0.1590902455516887</v>
+      </c>
+      <c r="S62">
+        <v>0.2084246284477436</v>
+      </c>
+      <c r="T62">
+        <v>0.2693941014419244</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>slope + BB</t>
+        </is>
+      </c>
+      <c r="E63">
+        <v>0.68</v>
+      </c>
+      <c r="F63">
+        <v>0.375</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H63">
+        <v>0.5093603968579351</v>
+      </c>
+      <c r="I63">
+        <v>0.2174998294134232</v>
+      </c>
+      <c r="J63">
+        <v>0.02538998049761626</v>
+      </c>
+      <c r="K63">
+        <v>0.5056210538686133</v>
+      </c>
+      <c r="L63">
+        <v>0.1436298659645323</v>
+      </c>
+      <c r="M63">
+        <v>0.1563675527661607</v>
+      </c>
+      <c r="N63">
+        <v>0.2303302454865548</v>
+      </c>
+      <c r="O63">
+        <v>0.3749350277917692</v>
+      </c>
+      <c r="P63">
+        <v>0.5056210538686133</v>
+      </c>
+      <c r="Q63">
+        <v>0.6484994494239853</v>
+      </c>
+      <c r="R63">
+        <v>0.7709436728222155</v>
+      </c>
+      <c r="S63">
+        <v>0.8604448264521787</v>
+      </c>
+      <c r="T63">
+        <v>0.9888076830100602</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>slope + BB</t>
+        </is>
+      </c>
+      <c r="E64">
+        <v>0.68</v>
+      </c>
+      <c r="F64">
+        <v>0.375</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H64">
+        <v>-1.266277759603915</v>
+      </c>
+      <c r="I64">
+        <v>0.8346447652605108</v>
+      </c>
+      <c r="J64">
+        <v>0.1606176425928626</v>
+      </c>
+      <c r="K64">
+        <v>-1.23201575320496</v>
+      </c>
+      <c r="L64">
+        <v>-2.840720392377818</v>
+      </c>
+      <c r="M64">
+        <v>-2.76987698365658</v>
+      </c>
+      <c r="N64">
+        <v>-2.431118794959679</v>
+      </c>
+      <c r="O64">
+        <v>-1.8369517251953</v>
+      </c>
+      <c r="P64">
+        <v>-1.23201575320496</v>
+      </c>
+      <c r="Q64">
+        <v>-0.6271849377994259</v>
+      </c>
+      <c r="R64">
+        <v>-0.2328525694455612</v>
+      </c>
+      <c r="S64">
+        <v>0.05194658859315354</v>
+      </c>
+      <c r="T64">
+        <v>0.1028185801768376</v>
       </c>
     </row>
   </sheetData>
@@ -4354,13 +6163,43 @@
         <v>1.16</v>
       </c>
       <c r="F3">
-        <v>1.162280701754386</v>
+        <v>1.587025747120549</v>
+      </c>
+      <c r="G3">
+        <v>0.004819815983976413</v>
+      </c>
+      <c r="H3">
+        <v>0.0009130476011032094</v>
       </c>
       <c r="I3">
-        <v>1.162280701754386</v>
+        <v>1.585474644036053</v>
+      </c>
+      <c r="J3">
+        <v>1.58246200949637</v>
+      </c>
+      <c r="K3">
+        <v>1.58246200949637</v>
+      </c>
+      <c r="L3">
+        <v>1.58343913351355</v>
+      </c>
+      <c r="M3">
+        <v>1.58343913351355</v>
       </c>
       <c r="N3">
-        <v>1.162280701754386</v>
+        <v>1.585474644036053</v>
+      </c>
+      <c r="O3">
+        <v>1.58994313995534</v>
+      </c>
+      <c r="P3">
+        <v>1.594535679080173</v>
+      </c>
+      <c r="Q3">
+        <v>1.596594035684137</v>
+      </c>
+      <c r="R3">
+        <v>1.603090300761623</v>
       </c>
     </row>
     <row r="4">
@@ -4384,13 +6223,43 @@
         <v>1.19</v>
       </c>
       <c r="F4">
-        <v>1.1875</v>
+        <v>1.643764768358514</v>
+      </c>
+      <c r="G4">
+        <v>0.0598150457305775</v>
+      </c>
+      <c r="H4">
+        <v>0.001135964182303611</v>
       </c>
       <c r="I4">
-        <v>1.1875</v>
+        <v>1.62481867079212</v>
+      </c>
+      <c r="J4">
+        <v>1.583912520471457</v>
+      </c>
+      <c r="K4">
+        <v>1.585839913193943</v>
+      </c>
+      <c r="L4">
+        <v>1.589168412353778</v>
+      </c>
+      <c r="M4">
+        <v>1.600698240816785</v>
       </c>
       <c r="N4">
-        <v>1.1875</v>
+        <v>1.62481867079212</v>
+      </c>
+      <c r="O4">
+        <v>1.668346547431238</v>
+      </c>
+      <c r="P4">
+        <v>1.724564317996106</v>
+      </c>
+      <c r="Q4">
+        <v>1.763997206655342</v>
+      </c>
+      <c r="R4">
+        <v>1.805946922280095</v>
       </c>
     </row>
     <row r="5">
@@ -4414,13 +6283,43 @@
         <v>1.06</v>
       </c>
       <c r="F5">
-        <v>1.063444108761329</v>
+        <v>1.60144902396862</v>
+      </c>
+      <c r="G5">
+        <v>0.01944436140980806</v>
+      </c>
+      <c r="H5">
+        <v>0.0003924310467100507</v>
       </c>
       <c r="I5">
-        <v>1.063444108761329</v>
+        <v>1.595428363725938</v>
+      </c>
+      <c r="J5">
+        <v>1.58253741826517</v>
+      </c>
+      <c r="K5">
+        <v>1.58306728535776</v>
+      </c>
+      <c r="L5">
+        <v>1.584211777589462</v>
+      </c>
+      <c r="M5">
+        <v>1.587552026953643</v>
       </c>
       <c r="N5">
-        <v>1.063444108761329</v>
+        <v>1.595428363725938</v>
+      </c>
+      <c r="O5">
+        <v>1.609089697790766</v>
+      </c>
+      <c r="P5">
+        <v>1.626600628382942</v>
+      </c>
+      <c r="Q5">
+        <v>1.640185858126406</v>
+      </c>
+      <c r="R5">
+        <v>1.654952132085821</v>
       </c>
     </row>
     <row r="6">
@@ -4444,13 +6343,43 @@
         <v>1.98</v>
       </c>
       <c r="F6">
-        <v>1.983606557377049</v>
+        <v>1.622332799330991</v>
+      </c>
+      <c r="G6">
+        <v>0.0411414067016729</v>
+      </c>
+      <c r="H6">
+        <v>0.005215741217277604</v>
       </c>
       <c r="I6">
-        <v>1.983606557377049</v>
+        <v>1.614455371034995</v>
+      </c>
+      <c r="J6">
+        <v>1.583563213038838</v>
+      </c>
+      <c r="K6">
+        <v>1.58482515001301</v>
+      </c>
+      <c r="L6">
+        <v>1.58619195383832</v>
+      </c>
+      <c r="M6">
+        <v>1.591811153580662</v>
       </c>
       <c r="N6">
-        <v>1.983606557377049</v>
+        <v>1.614455371034995</v>
+      </c>
+      <c r="O6">
+        <v>1.635130237477513</v>
+      </c>
+      <c r="P6">
+        <v>1.70114045187836</v>
+      </c>
+      <c r="Q6">
+        <v>1.714015488909228</v>
+      </c>
+      <c r="R6">
+        <v>1.72610416796955</v>
       </c>
     </row>
   </sheetData>
@@ -6038,37 +7967,43 @@
         </is>
       </c>
       <c r="H2">
-        <v>-1.09167266865871</v>
+        <v>-0.8343754707424136</v>
+      </c>
+      <c r="I2">
+        <v>0.2848731536250926</v>
+      </c>
+      <c r="J2">
+        <v>0.1318117273209451</v>
       </c>
       <c r="K2">
-        <v>-1.09167266865871</v>
+        <v>-0.834971772416631</v>
       </c>
       <c r="L2">
-        <v>-1.81910917878443</v>
+        <v>-1.272171912047676</v>
       </c>
       <c r="M2">
-        <v>-1.70354713493108</v>
+        <v>-1.243040391847961</v>
       </c>
       <c r="N2">
-        <v>-1.54818264596463</v>
+        <v>-1.208698155799748</v>
       </c>
       <c r="O2">
-        <v>-1.33755752736795</v>
+        <v>-1.052457822131593</v>
       </c>
       <c r="P2">
-        <v>-1.09167266865871</v>
+        <v>-0.834971772416631</v>
       </c>
       <c r="Q2">
-        <v>-0.849687775154425</v>
+        <v>-0.5835761419880313</v>
       </c>
       <c r="R2">
-        <v>-0.624431270945473</v>
+        <v>-0.4481062700124688</v>
       </c>
       <c r="S2">
-        <v>-0.497658747917406</v>
+        <v>-0.426372315667659</v>
       </c>
       <c r="T2">
-        <v>-0.383243888804548</v>
+        <v>-0.3712083330414118</v>
       </c>
     </row>
     <row r="3">
@@ -6102,37 +8037,43 @@
         </is>
       </c>
       <c r="H3">
-        <v>0.0383486757232204</v>
+        <v>0.1666347000990206</v>
+      </c>
+      <c r="I3">
+        <v>0.2216982370608659</v>
+      </c>
+      <c r="J3">
+        <v>0.07268657435264894</v>
       </c>
       <c r="K3">
-        <v>0.0383486757232204</v>
+        <v>0.1343873165366745</v>
       </c>
       <c r="L3">
-        <v>-0.605589256817529</v>
+        <v>-0.2524574607495085</v>
       </c>
       <c r="M3">
-        <v>-0.479547144435942</v>
+        <v>-0.1340495786478707</v>
       </c>
       <c r="N3">
-        <v>-0.362855458173382</v>
+        <v>-0.08954350469411443</v>
       </c>
       <c r="O3">
-        <v>-0.164258778801576</v>
+        <v>0.02352968132968275</v>
       </c>
       <c r="P3">
-        <v>0.0383486757232204</v>
+        <v>0.1343873165366745</v>
       </c>
       <c r="Q3">
-        <v>0.24985097619763</v>
+        <v>0.2922957698564618</v>
       </c>
       <c r="R3">
-        <v>0.449145511837017</v>
+        <v>0.5113550234708423</v>
       </c>
       <c r="S3">
-        <v>0.558891168197361</v>
+        <v>0.5591394586229723</v>
       </c>
       <c r="T3">
-        <v>0.655691094910271</v>
+        <v>0.6077455854179703</v>
       </c>
     </row>
     <row r="4">
@@ -6166,37 +8107,43 @@
         </is>
       </c>
       <c r="H4">
-        <v>-1.13091338627302</v>
+        <v>-1.152656882502407</v>
+      </c>
+      <c r="I4">
+        <v>0.1534220233378837</v>
+      </c>
+      <c r="J4">
+        <v>0.02667379745960026</v>
       </c>
       <c r="K4">
-        <v>-1.13091338627302</v>
+        <v>-1.164409210368508</v>
       </c>
       <c r="L4">
-        <v>-1.80071408294041</v>
+        <v>-1.531342575457185</v>
       </c>
       <c r="M4">
-        <v>-1.70104439990101</v>
+        <v>-1.41036055968669</v>
       </c>
       <c r="N4">
-        <v>-1.59470414093948</v>
+        <v>-1.34747180972</v>
       </c>
       <c r="O4">
-        <v>-1.3728432692903</v>
+        <v>-1.224940057495803</v>
       </c>
       <c r="P4">
-        <v>-1.13091338627302</v>
+        <v>-1.164409210368508</v>
       </c>
       <c r="Q4">
-        <v>-0.935385829781613</v>
+        <v>-1.043609254764194</v>
       </c>
       <c r="R4">
-        <v>-0.753448891671335</v>
+        <v>-0.9599176884694822</v>
       </c>
       <c r="S4">
-        <v>-0.637918343032296</v>
+        <v>-0.9144199906028663</v>
       </c>
       <c r="T4">
-        <v>-0.52948118187852</v>
+        <v>-0.9008671911962983</v>
       </c>
     </row>
     <row r="5">
@@ -6230,37 +8177,43 @@
         </is>
       </c>
       <c r="H5">
-        <v>-2.36555332023772</v>
+        <v>-2.211594343673157</v>
+      </c>
+      <c r="I5">
+        <v>0.2230004440914079</v>
+      </c>
+      <c r="J5">
+        <v>0.1055656189432634</v>
       </c>
       <c r="K5">
-        <v>-2.36555332023772</v>
+        <v>-2.261254392023111</v>
       </c>
       <c r="L5">
-        <v>-3.08409709344872</v>
+        <v>-2.631169242103466</v>
       </c>
       <c r="M5">
-        <v>-2.98600521570151</v>
+        <v>-2.574233158527166</v>
       </c>
       <c r="N5">
-        <v>-2.87076003583092</v>
+        <v>-2.478442942875799</v>
       </c>
       <c r="O5">
-        <v>-2.64612271540245</v>
+        <v>-2.379584904008128</v>
       </c>
       <c r="P5">
-        <v>-2.36555332023772</v>
+        <v>-2.261254392023111</v>
       </c>
       <c r="Q5">
-        <v>-2.09301955461122</v>
+        <v>-2.065333990778402</v>
       </c>
       <c r="R5">
-        <v>-1.86205152724641</v>
+        <v>-1.860650147893161</v>
       </c>
       <c r="S5">
-        <v>-1.68597235582323</v>
+        <v>-1.783263279018806</v>
       </c>
       <c r="T5">
-        <v>-1.5512985289048</v>
+        <v>-1.769872645678602</v>
       </c>
     </row>
     <row r="6">
@@ -6294,37 +8247,43 @@
         </is>
       </c>
       <c r="H6">
-        <v>-1.33250538428134</v>
+        <v>-2.097587353880819</v>
+      </c>
+      <c r="I6">
+        <v>0.8651976283011569</v>
+      </c>
+      <c r="J6">
+        <v>0.2518497575176931</v>
       </c>
       <c r="K6">
-        <v>-1.33250538428134</v>
+        <v>-2.021166403046479</v>
       </c>
       <c r="L6">
-        <v>-3.52159165659489</v>
+        <v>-3.89025328560212</v>
       </c>
       <c r="M6">
-        <v>-3.10176596914126</v>
+        <v>-3.641075236959403</v>
       </c>
       <c r="N6">
-        <v>-2.64507377355787</v>
+        <v>-3.197472366120072</v>
       </c>
       <c r="O6">
-        <v>-1.98656705841723</v>
+        <v>-2.827192751717598</v>
       </c>
       <c r="P6">
-        <v>-1.33250538428134</v>
+        <v>-2.021166403046479</v>
       </c>
       <c r="Q6">
-        <v>-0.761155302700917</v>
+        <v>-1.3729525806744</v>
       </c>
       <c r="R6">
-        <v>-0.316917482082253</v>
+        <v>-0.9651058538183455</v>
       </c>
       <c r="S6">
-        <v>-0.105762141666758</v>
+        <v>-0.884137529495442</v>
       </c>
       <c r="T6">
-        <v>0.041226650217689</v>
+        <v>-0.7262242602939739</v>
       </c>
     </row>
     <row r="7">
@@ -6358,37 +8317,43 @@
         </is>
       </c>
       <c r="H7">
-        <v>-0.48332502924255</v>
+        <v>-0.5510156381020054</v>
+      </c>
+      <c r="I7">
+        <v>0.3290178164927073</v>
+      </c>
+      <c r="J7">
+        <v>0.05456015077725753</v>
       </c>
       <c r="K7">
-        <v>-0.48332502924255</v>
+        <v>-0.5157394755421896</v>
       </c>
       <c r="L7">
-        <v>-1.88251285338097</v>
+        <v>-1.272737071453193</v>
       </c>
       <c r="M7">
-        <v>-1.57869205452822</v>
+        <v>-1.181335563467513</v>
       </c>
       <c r="N7">
-        <v>-1.28717378662065</v>
+        <v>-0.957162199504825</v>
       </c>
       <c r="O7">
-        <v>-0.875138998281031</v>
+        <v>-0.739647846328114</v>
       </c>
       <c r="P7">
-        <v>-0.48332502924255</v>
+        <v>-0.5157394755421896</v>
       </c>
       <c r="Q7">
-        <v>-0.212050341449445</v>
+        <v>-0.3572558492900185</v>
       </c>
       <c r="R7">
-        <v>0.009144392998675741</v>
+        <v>-0.1185068443429195</v>
       </c>
       <c r="S7">
-        <v>0.116518615320811</v>
+        <v>-0.03209639160380096</v>
       </c>
       <c r="T7">
-        <v>0.207180904763053</v>
+        <v>0.02911554702556507</v>
       </c>
     </row>
     <row r="8">
@@ -6422,37 +8387,43 @@
         </is>
       </c>
       <c r="H8">
-        <v>-0.8540081936545471</v>
+        <v>-0.7307667586694649</v>
+      </c>
+      <c r="I8">
+        <v>0.2711093592647267</v>
+      </c>
+      <c r="J8">
+        <v>0.1344028879325774</v>
       </c>
       <c r="K8">
-        <v>-0.8540081936545471</v>
+        <v>-0.7123076567262183</v>
       </c>
       <c r="L8">
-        <v>-1.51347226325948</v>
+        <v>-1.13625589975834</v>
       </c>
       <c r="M8">
-        <v>-1.42738640250991</v>
+        <v>-1.10132975232478</v>
       </c>
       <c r="N8">
-        <v>-1.30718251841308</v>
+        <v>-1.077469438244685</v>
       </c>
       <c r="O8">
-        <v>-1.09077646111523</v>
+        <v>-0.9684247740413162</v>
       </c>
       <c r="P8">
-        <v>-0.8540081936545471</v>
+        <v>-0.7123076567262183</v>
       </c>
       <c r="Q8">
-        <v>-0.634244442608356</v>
+        <v>-0.5269421038278028</v>
       </c>
       <c r="R8">
-        <v>-0.44608111243012</v>
+        <v>-0.3206197185541889</v>
       </c>
       <c r="S8">
-        <v>-0.329303540792073</v>
+        <v>-0.2190351026446799</v>
       </c>
       <c r="T8">
-        <v>-0.235589287348351</v>
+        <v>-0.2190351026446799</v>
       </c>
     </row>
     <row r="9">
@@ -6486,37 +8457,43 @@
         </is>
       </c>
       <c r="H9">
-        <v>-1.26330521503005</v>
+        <v>-1.177724120277592</v>
+      </c>
+      <c r="I9">
+        <v>0.1368646713877105</v>
+      </c>
+      <c r="J9">
+        <v>0.02481612889605708</v>
       </c>
       <c r="K9">
-        <v>-1.26330521503005</v>
+        <v>-1.194016191431254</v>
       </c>
       <c r="L9">
-        <v>-1.78171494226729</v>
+        <v>-1.395478038275788</v>
       </c>
       <c r="M9">
-        <v>-1.70578289831481</v>
+        <v>-1.382069213708613</v>
       </c>
       <c r="N9">
-        <v>-1.61401260953999</v>
+        <v>-1.352111583967158</v>
       </c>
       <c r="O9">
-        <v>-1.45948188364552</v>
+        <v>-1.277066351409607</v>
       </c>
       <c r="P9">
-        <v>-1.26330521503005</v>
+        <v>-1.194016191431254</v>
       </c>
       <c r="Q9">
-        <v>-1.06003488174625</v>
+        <v>-1.088914660138022</v>
       </c>
       <c r="R9">
-        <v>-0.886918143414686</v>
+        <v>-0.9682120362962292</v>
       </c>
       <c r="S9">
-        <v>-0.796820610141294</v>
+        <v>-0.9441014632173645</v>
       </c>
       <c r="T9">
-        <v>-0.7057987699471751</v>
+        <v>-0.8822498673889991</v>
       </c>
     </row>
     <row r="10">
@@ -6550,37 +8527,43 @@
         </is>
       </c>
       <c r="H10">
-        <v>-2.34237891611451</v>
+        <v>-2.183381184170333</v>
+      </c>
+      <c r="I10">
+        <v>0.1707842885476979</v>
+      </c>
+      <c r="J10">
+        <v>0.06724572168354724</v>
       </c>
       <c r="K10">
-        <v>-2.34237891611451</v>
+        <v>-2.19042616286217</v>
       </c>
       <c r="L10">
-        <v>-2.87413301958752</v>
+        <v>-2.483612123412183</v>
       </c>
       <c r="M10">
-        <v>-2.7885313052878</v>
+        <v>-2.483485409434572</v>
       </c>
       <c r="N10">
-        <v>-2.69921052975566</v>
+        <v>-2.421520067693024</v>
       </c>
       <c r="O10">
-        <v>-2.53029447273778</v>
+        <v>-2.285019101803254</v>
       </c>
       <c r="P10">
-        <v>-2.34237891611451</v>
+        <v>-2.19042616286217</v>
       </c>
       <c r="Q10">
-        <v>-2.14821170117781</v>
+        <v>-2.074715340740159</v>
       </c>
       <c r="R10">
-        <v>-1.98460043599753</v>
+        <v>-1.899841240683838</v>
       </c>
       <c r="S10">
-        <v>-1.88665661375306</v>
+        <v>-1.865669371039645</v>
       </c>
       <c r="T10">
-        <v>-1.77011861743285</v>
+        <v>-1.865669371039645</v>
       </c>
     </row>
     <row r="11">
@@ -6614,37 +8597,43 @@
         </is>
       </c>
       <c r="H11">
-        <v>-1.42936862427318</v>
+        <v>-1.828658726768258</v>
+      </c>
+      <c r="I11">
+        <v>0.8207240677098363</v>
+      </c>
+      <c r="J11">
+        <v>0.2792716561825207</v>
       </c>
       <c r="K11">
-        <v>-1.42936862427318</v>
+        <v>-1.63565078000148</v>
       </c>
       <c r="L11">
-        <v>-3.37361234570619</v>
+        <v>-3.703724220311459</v>
       </c>
       <c r="M11">
-        <v>-3.01189216714425</v>
+        <v>-3.47891583890407</v>
       </c>
       <c r="N11">
-        <v>-2.69636197596794</v>
+        <v>-3.057503523505131</v>
       </c>
       <c r="O11">
-        <v>-2.10789862175422</v>
+        <v>-2.362750045495978</v>
       </c>
       <c r="P11">
-        <v>-1.42936862427318</v>
+        <v>-1.63565078000148</v>
       </c>
       <c r="Q11">
-        <v>-0.872494575029033</v>
+        <v>-1.255605029209338</v>
       </c>
       <c r="R11">
-        <v>-0.448601518037732</v>
+        <v>-0.8898094956368673</v>
       </c>
       <c r="S11">
-        <v>-0.209594269697237</v>
+        <v>-0.6199082577582717</v>
       </c>
       <c r="T11">
-        <v>-0.0405360362422776</v>
+        <v>-0.5957311636908798</v>
       </c>
     </row>
     <row r="12">
@@ -6678,37 +8667,43 @@
         </is>
       </c>
       <c r="H12">
-        <v>-1.02018854438725</v>
+        <v>-0.5411538283408674</v>
+      </c>
+      <c r="I12">
+        <v>0.1934066469517847</v>
+      </c>
+      <c r="J12">
+        <v>0.07114251696824865</v>
       </c>
       <c r="K12">
-        <v>-1.02018854438725</v>
+        <v>-0.5498953132538859</v>
       </c>
       <c r="L12">
-        <v>-1.80728672852912</v>
+        <v>-0.8241269743819788</v>
       </c>
       <c r="M12">
-        <v>-1.6557400582839</v>
+        <v>-0.818189057612336</v>
       </c>
       <c r="N12">
-        <v>-1.4952674321361</v>
+        <v>-0.7818787488197412</v>
       </c>
       <c r="O12">
-        <v>-1.26020248957157</v>
+        <v>-0.7275035718906924</v>
       </c>
       <c r="P12">
-        <v>-1.02018854438725</v>
+        <v>-0.5498953132538859</v>
       </c>
       <c r="Q12">
-        <v>-0.796169084647451</v>
+        <v>-0.357563126834899</v>
       </c>
       <c r="R12">
-        <v>-0.593037921766594</v>
+        <v>-0.2885659161026625</v>
       </c>
       <c r="S12">
-        <v>-0.471489095434699</v>
+        <v>-0.2604523542345711</v>
       </c>
       <c r="T12">
-        <v>-0.363277510744215</v>
+        <v>-0.2086753291202262</v>
       </c>
     </row>
     <row r="13">
@@ -6742,37 +8737,43 @@
         </is>
       </c>
       <c r="H13">
-        <v>-1.22010381494236</v>
+        <v>-1.010819589280612</v>
+      </c>
+      <c r="I13">
+        <v>0.2251398323717008</v>
+      </c>
+      <c r="J13">
+        <v>0.06482858120536823</v>
       </c>
       <c r="K13">
-        <v>-1.22010381494236</v>
+        <v>-1.035188141484134</v>
       </c>
       <c r="L13">
-        <v>-1.80476614581316</v>
+        <v>-1.383410554548667</v>
       </c>
       <c r="M13">
-        <v>-1.72227014646008</v>
+        <v>-1.314317961004864</v>
       </c>
       <c r="N13">
-        <v>-1.60936725369676</v>
+        <v>-1.260350933013959</v>
       </c>
       <c r="O13">
-        <v>-1.42737156436513</v>
+        <v>-1.181524690764977</v>
       </c>
       <c r="P13">
-        <v>-1.22010381494236</v>
+        <v>-1.035188141484134</v>
       </c>
       <c r="Q13">
-        <v>-1.0214572073894</v>
+        <v>-0.8905037791611714</v>
       </c>
       <c r="R13">
-        <v>-0.843212934590748</v>
+        <v>-0.7788305210909211</v>
       </c>
       <c r="S13">
-        <v>-0.724676576738432</v>
+        <v>-0.4798134021950344</v>
       </c>
       <c r="T13">
-        <v>-0.614861237544844</v>
+        <v>-0.4563092624652844</v>
       </c>
     </row>
     <row r="14">
@@ -6806,37 +8807,43 @@
         </is>
       </c>
       <c r="H14">
-        <v>-2.21560202854327</v>
+        <v>-1.956175385055819</v>
+      </c>
+      <c r="I14">
+        <v>0.2579258938796519</v>
+      </c>
+      <c r="J14">
+        <v>0.1095358050906857</v>
       </c>
       <c r="K14">
-        <v>-2.21560202854327</v>
+        <v>-2.048337711515549</v>
       </c>
       <c r="L14">
-        <v>-2.91103249588617</v>
+        <v>-2.269812550053572</v>
       </c>
       <c r="M14">
-        <v>-2.80631746499368</v>
+        <v>-2.263588028867993</v>
       </c>
       <c r="N14">
-        <v>-2.66667039908178</v>
+        <v>-2.197305032928032</v>
       </c>
       <c r="O14">
-        <v>-2.44369159131239</v>
+        <v>-2.141065974232298</v>
       </c>
       <c r="P14">
-        <v>-2.21560202854327</v>
+        <v>-2.048337711515549</v>
       </c>
       <c r="Q14">
-        <v>-2.03286610009253</v>
+        <v>-1.823437846127612</v>
       </c>
       <c r="R14">
-        <v>-1.85973588321558</v>
+        <v>-1.659450972852719</v>
       </c>
       <c r="S14">
-        <v>-1.73804266214156</v>
+        <v>-1.257892346222186</v>
       </c>
       <c r="T14">
-        <v>-1.63365409182055</v>
+        <v>-1.191574795635222</v>
       </c>
     </row>
     <row r="15">
@@ -6870,37 +8877,43 @@
         </is>
       </c>
       <c r="H15">
-        <v>-1.72176479188108</v>
+        <v>-1.459230838703992</v>
+      </c>
+      <c r="I15">
+        <v>0.4777576664002882</v>
+      </c>
+      <c r="J15">
+        <v>0.08529618837960391</v>
       </c>
       <c r="K15">
-        <v>-1.72176479188108</v>
+        <v>-1.366926788490725</v>
       </c>
       <c r="L15">
-        <v>-4.33356582005306</v>
+        <v>-2.489786496817119</v>
       </c>
       <c r="M15">
-        <v>-3.73466299556028</v>
+        <v>-2.298774975130094</v>
       </c>
       <c r="N15">
-        <v>-3.21355098928141</v>
+        <v>-2.116852360211993</v>
       </c>
       <c r="O15">
-        <v>-2.48717880799542</v>
+        <v>-1.793823604619208</v>
       </c>
       <c r="P15">
-        <v>-1.72176479188108</v>
+        <v>-1.366926788490725</v>
       </c>
       <c r="Q15">
-        <v>-1.01918963184879</v>
+        <v>-1.128836226710184</v>
       </c>
       <c r="R15">
-        <v>-0.484894237710295</v>
+        <v>-0.885616211241669</v>
       </c>
       <c r="S15">
-        <v>-0.207075116931636</v>
+        <v>-0.7368495039814162</v>
       </c>
       <c r="T15">
-        <v>-0.0682909392804618</v>
+        <v>-0.6658932631656005</v>
       </c>
     </row>
     <row r="16">
@@ -6934,37 +8947,43 @@
         </is>
       </c>
       <c r="H16">
-        <v>-0.580310053605375</v>
+        <v>-0.4205532588851846</v>
+      </c>
+      <c r="I16">
+        <v>0.3085782102603682</v>
+      </c>
+      <c r="J16">
+        <v>0.05885893839320223</v>
       </c>
       <c r="K16">
-        <v>-0.580310053605375</v>
+        <v>-0.3589789550319535</v>
       </c>
       <c r="L16">
-        <v>-2.1287663829272</v>
+        <v>-1.37624127345034</v>
       </c>
       <c r="M16">
-        <v>-1.82030933512784</v>
+        <v>-0.9284289663258757</v>
       </c>
       <c r="N16">
-        <v>-1.49189950795506</v>
+        <v>-0.7475488337204534</v>
       </c>
       <c r="O16">
-        <v>-1.00269206829709</v>
+        <v>-0.6012722334420149</v>
       </c>
       <c r="P16">
-        <v>-0.580310053605375</v>
+        <v>-0.3589789550319535</v>
       </c>
       <c r="Q16">
-        <v>-0.256392796445441</v>
+        <v>-0.2052124264072147</v>
       </c>
       <c r="R16">
-        <v>-0.0285208587641077</v>
+        <v>-0.1096284111204457</v>
       </c>
       <c r="S16">
-        <v>0.09828884157455541</v>
+        <v>-0.05998842837792913</v>
       </c>
       <c r="T16">
-        <v>0.195668832424048</v>
+        <v>-0.02030566477183715</v>
       </c>
     </row>
   </sheetData>
@@ -6974,7 +8993,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7106,41 +9125,47 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_ndvi_cv</t>
         </is>
       </c>
       <c r="H2">
-        <v>-1.77550211362218</v>
+        <v>0.8337359854465328</v>
+      </c>
+      <c r="I2">
+        <v>0.7380390476713603</v>
+      </c>
+      <c r="J2">
+        <v>0.02844388581785389</v>
       </c>
       <c r="K2">
-        <v>-1.77550211362218</v>
+        <v>0.9230883691996279</v>
       </c>
       <c r="L2">
-        <v>-2.92805228954337</v>
+        <v>-1.342559700887139</v>
       </c>
       <c r="M2">
-        <v>-2.68365474742128</v>
+        <v>-0.5293593826140167</v>
       </c>
       <c r="N2">
-        <v>-2.42720851528167</v>
+        <v>0.1992485863476329</v>
       </c>
       <c r="O2">
-        <v>-2.08805416610993</v>
+        <v>0.5882405310485335</v>
       </c>
       <c r="P2">
-        <v>-1.77550211362218</v>
+        <v>0.9230883691996279</v>
       </c>
       <c r="Q2">
-        <v>-1.45487540780859</v>
+        <v>1.221989431438493</v>
       </c>
       <c r="R2">
-        <v>-1.15334022064003</v>
+        <v>1.504887118970426</v>
       </c>
       <c r="S2">
-        <v>-0.991704409058911</v>
+        <v>1.713008515343956</v>
       </c>
       <c r="T2">
-        <v>-0.889084701812326</v>
+        <v>1.91663993128164</v>
       </c>
     </row>
     <row r="3">
@@ -7170,41 +9195,47 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H3">
-        <v>1.12540019655818</v>
+        <v>-0.3806288059268695</v>
+      </c>
+      <c r="I3">
+        <v>1.136733883711535</v>
+      </c>
+      <c r="J3">
+        <v>0.02995669114975803</v>
       </c>
       <c r="K3">
-        <v>1.12540019655818</v>
+        <v>-0.5821611307596413</v>
       </c>
       <c r="L3">
-        <v>0.206790378027343</v>
+        <v>-2.376804979109037</v>
       </c>
       <c r="M3">
-        <v>0.328674427925573</v>
+        <v>-1.873883017290939</v>
       </c>
       <c r="N3">
-        <v>0.48026954239893</v>
+        <v>-1.509770142132372</v>
       </c>
       <c r="O3">
-        <v>0.7728398604873939</v>
+        <v>-1.035017637596761</v>
       </c>
       <c r="P3">
-        <v>1.12540019655818</v>
+        <v>-0.5821611307596413</v>
       </c>
       <c r="Q3">
-        <v>1.43801732597714</v>
+        <v>0.05298732917228682</v>
       </c>
       <c r="R3">
-        <v>1.79491255631904</v>
+        <v>1.213978036728389</v>
       </c>
       <c r="S3">
-        <v>2.06651009407335</v>
+        <v>1.912291546120434</v>
       </c>
       <c r="T3">
-        <v>2.32491558042549</v>
+        <v>2.429291883239949</v>
       </c>
     </row>
     <row r="4">
@@ -7234,41 +9265,47 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H4">
-        <v>-0.285354992876321</v>
+        <v>0.6229935946048304</v>
+      </c>
+      <c r="I4">
+        <v>0.9488182407534228</v>
+      </c>
+      <c r="J4">
+        <v>0.032185399299025</v>
       </c>
       <c r="K4">
-        <v>-0.285354992876321</v>
+        <v>0.7849902698081848</v>
       </c>
       <c r="L4">
-        <v>-1.20933735478135</v>
+        <v>-2.115349662222658</v>
       </c>
       <c r="M4">
-        <v>-1.07691701560579</v>
+        <v>-1.385249644667364</v>
       </c>
       <c r="N4">
-        <v>-0.915513828747217</v>
+        <v>-0.4937873193970266</v>
       </c>
       <c r="O4">
-        <v>-0.603673786409283</v>
+        <v>0.4185501645629774</v>
       </c>
       <c r="P4">
-        <v>-0.285354992876321</v>
+        <v>0.7849902698081848</v>
       </c>
       <c r="Q4">
-        <v>0.00776062855076141</v>
+        <v>1.098737734738604</v>
       </c>
       <c r="R4">
-        <v>0.272561540916779</v>
+        <v>1.398122505638628</v>
       </c>
       <c r="S4">
-        <v>0.416080160200481</v>
+        <v>1.635025216621362</v>
       </c>
       <c r="T4">
-        <v>0.544822185744366</v>
+        <v>2.138885356616776</v>
       </c>
     </row>
     <row r="5">
@@ -7278,7 +9315,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7287,52 +9324,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ndvi_cv + elev + DE</t>
+          <t>ndvi_cv + elev + BB + DE</t>
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F5">
-        <v>0.661</v>
+        <v>0.296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>beta_DE</t>
+          <t>beta_ndvi_cv</t>
         </is>
       </c>
       <c r="H5">
-        <v>1.05065352262729</v>
+        <v>0.8002416545302975</v>
+      </c>
+      <c r="I5">
+        <v>0.7700066559454261</v>
+      </c>
+      <c r="J5">
+        <v>0.03204582605609804</v>
       </c>
       <c r="K5">
-        <v>1.05065352262729</v>
+        <v>0.9047760017188051</v>
       </c>
       <c r="L5">
-        <v>0.217460982256379</v>
+        <v>-1.514767739662864</v>
       </c>
       <c r="M5">
-        <v>0.355591419265951</v>
+        <v>-0.7262525901310021</v>
       </c>
       <c r="N5">
-        <v>0.513018823524845</v>
+        <v>0.165906721491429</v>
       </c>
       <c r="O5">
-        <v>0.766116846187338</v>
+        <v>0.5886160595071621</v>
       </c>
       <c r="P5">
-        <v>1.05065352262729</v>
+        <v>0.9047760017188051</v>
       </c>
       <c r="Q5">
-        <v>1.32511787072351</v>
+        <v>1.193656752042501</v>
       </c>
       <c r="R5">
-        <v>1.56909143123296</v>
+        <v>1.482927105977661</v>
       </c>
       <c r="S5">
-        <v>1.73400215757066</v>
+        <v>1.674904271739513</v>
       </c>
       <c r="T5">
-        <v>1.87544188930189</v>
+        <v>1.883553567924814</v>
       </c>
     </row>
     <row r="6">
@@ -7362,41 +9405,47 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H6">
-        <v>-1.92829098084159</v>
+        <v>-0.4516004966752659</v>
+      </c>
+      <c r="I6">
+        <v>1.108418499790955</v>
+      </c>
+      <c r="J6">
+        <v>0.03351978242951942</v>
       </c>
       <c r="K6">
-        <v>-1.92829098084159</v>
+        <v>-0.6277626170031898</v>
       </c>
       <c r="L6">
-        <v>-3.08733105521218</v>
+        <v>-2.426078291355212</v>
       </c>
       <c r="M6">
-        <v>-2.88933847760348</v>
+        <v>-1.960354953096786</v>
       </c>
       <c r="N6">
-        <v>-2.6530236126615</v>
+        <v>-1.570689684543826</v>
       </c>
       <c r="O6">
-        <v>-2.28982282453145</v>
+        <v>-1.067519594187461</v>
       </c>
       <c r="P6">
-        <v>-1.92829098084159</v>
+        <v>-0.6277626170031898</v>
       </c>
       <c r="Q6">
-        <v>-1.6042154412775</v>
+        <v>-0.004170207489960706</v>
       </c>
       <c r="R6">
-        <v>-1.32061197355128</v>
+        <v>1.061512540448699</v>
       </c>
       <c r="S6">
-        <v>-1.14415817760739</v>
+        <v>1.716949596040392</v>
       </c>
       <c r="T6">
-        <v>-1.02285752781691</v>
+        <v>2.247716469837891</v>
       </c>
     </row>
     <row r="7">
@@ -7426,41 +9475,47 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>beta_ndvi_cv</t>
+          <t>beta_BB</t>
         </is>
       </c>
       <c r="H7">
-        <v>1.01413155993839</v>
+        <v>-0.6882130015174528</v>
+      </c>
+      <c r="I7">
+        <v>1.327063815072432</v>
+      </c>
+      <c r="J7">
+        <v>0.02476917652404654</v>
       </c>
       <c r="K7">
-        <v>1.01413155993839</v>
+        <v>-0.7702038729864665</v>
       </c>
       <c r="L7">
-        <v>0.132900404782863</v>
+        <v>-3.107214292744872</v>
       </c>
       <c r="M7">
-        <v>0.271945605126318</v>
+        <v>-2.697527175911463</v>
       </c>
       <c r="N7">
-        <v>0.421471846975689</v>
+        <v>-2.240661308673004</v>
       </c>
       <c r="O7">
-        <v>0.702677718412927</v>
+        <v>-1.518850158866036</v>
       </c>
       <c r="P7">
-        <v>1.01413155993839</v>
+        <v>-0.7702038729864665</v>
       </c>
       <c r="Q7">
-        <v>1.30765743401912</v>
+        <v>-0.05904362354368731</v>
       </c>
       <c r="R7">
-        <v>1.62045341082267</v>
+        <v>1.109443595377192</v>
       </c>
       <c r="S7">
-        <v>1.76983604142117</v>
+        <v>1.810098799883983</v>
       </c>
       <c r="T7">
-        <v>1.90879541650357</v>
+        <v>2.372299713557679</v>
       </c>
     </row>
     <row r="8">
@@ -7490,169 +9545,47 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>beta_elev</t>
+          <t>beta_DE</t>
         </is>
       </c>
       <c r="H8">
-        <v>-0.495414542564131</v>
+        <v>0.6078452414098873</v>
+      </c>
+      <c r="I8">
+        <v>0.8864471303677438</v>
+      </c>
+      <c r="J8">
+        <v>0.0289047566794842</v>
       </c>
       <c r="K8">
-        <v>-0.495414542564131</v>
+        <v>0.7653375111660087</v>
       </c>
       <c r="L8">
-        <v>-1.52362447306495</v>
+        <v>-1.964062183754407</v>
       </c>
       <c r="M8">
-        <v>-1.35148821329627</v>
+        <v>-1.210673644941546</v>
       </c>
       <c r="N8">
-        <v>-1.1499129184622</v>
+        <v>-0.3246582539694939</v>
       </c>
       <c r="O8">
-        <v>-0.840610206815118</v>
+        <v>0.4213195500666771</v>
       </c>
       <c r="P8">
-        <v>-0.495414542564131</v>
+        <v>0.7653375111660087</v>
       </c>
       <c r="Q8">
-        <v>-0.125089258009898</v>
+        <v>1.046327088889025</v>
       </c>
       <c r="R8">
-        <v>0.159536350908174</v>
+        <v>1.322294322080186</v>
       </c>
       <c r="S8">
-        <v>0.31770835673824</v>
+        <v>1.551629891125228</v>
       </c>
       <c r="T8">
-        <v>0.436517430999924</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gaur</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Spatial</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ndvi_cv + elev + BB + DE</t>
-        </is>
-      </c>
-      <c r="E9">
-        <v>1.6</v>
-      </c>
-      <c r="F9">
-        <v>0.296</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>beta_BB</t>
-        </is>
-      </c>
-      <c r="H9">
-        <v>-0.994737806540444</v>
-      </c>
-      <c r="K9">
-        <v>-0.994737806540444</v>
-      </c>
-      <c r="L9">
-        <v>-3.11308461045173</v>
-      </c>
-      <c r="M9">
-        <v>-2.71268071408547</v>
-      </c>
-      <c r="N9">
-        <v>-2.29658945325533</v>
-      </c>
-      <c r="O9">
-        <v>-1.64161849070535</v>
-      </c>
-      <c r="P9">
-        <v>-0.994737806540444</v>
-      </c>
-      <c r="Q9">
-        <v>-0.491034043491208</v>
-      </c>
-      <c r="R9">
-        <v>-0.176470337211962</v>
-      </c>
-      <c r="S9">
-        <v>-0.0165683824464211</v>
-      </c>
-      <c r="T9">
-        <v>0.117959738747891</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Gaur</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Spatial</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ndvi_cv + elev + BB + DE</t>
-        </is>
-      </c>
-      <c r="E10">
-        <v>1.6</v>
-      </c>
-      <c r="F10">
-        <v>0.296</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>beta_DE</t>
-        </is>
-      </c>
-      <c r="H10">
-        <v>0.98589967797526</v>
-      </c>
-      <c r="K10">
-        <v>0.98589967797526</v>
-      </c>
-      <c r="L10">
-        <v>0.221613566732788</v>
-      </c>
-      <c r="M10">
-        <v>0.338495997281448</v>
-      </c>
-      <c r="N10">
-        <v>0.507922104059593</v>
-      </c>
-      <c r="O10">
-        <v>0.739916958861019</v>
-      </c>
-      <c r="P10">
-        <v>0.98589967797526</v>
-      </c>
-      <c r="Q10">
-        <v>1.23545753454557</v>
-      </c>
-      <c r="R10">
-        <v>1.45641958361124</v>
-      </c>
-      <c r="S10">
-        <v>1.61041658025457</v>
-      </c>
-      <c r="T10">
-        <v>1.72944319952983</v>
+        <v>1.840835948911052</v>
       </c>
     </row>
   </sheetData>
@@ -7662,7 +9595,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7774,61 +9707,67 @@
         </is>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>elev + slope</t>
         </is>
       </c>
       <c r="E2">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.08599999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>beta0 (Intercept)</t>
+          <t>beta_elev</t>
         </is>
       </c>
       <c r="H2">
-        <v>1.07405140668518</v>
+        <v>-0.0544196745399779</v>
+      </c>
+      <c r="I2">
+        <v>1.294775909300191</v>
+      </c>
+      <c r="J2">
+        <v>0.01789030466328016</v>
       </c>
       <c r="K2">
-        <v>1.07405140668518</v>
+        <v>-0.1638780530671466</v>
       </c>
       <c r="L2">
-        <v>0.817777021540115</v>
+        <v>-2.750483851184881</v>
       </c>
       <c r="M2">
-        <v>0.853175454069559</v>
+        <v>-2.249706084120765</v>
       </c>
       <c r="N2">
-        <v>0.897540703585668</v>
+        <v>-1.649595864376685</v>
       </c>
       <c r="O2">
-        <v>0.982225773153378</v>
+        <v>-0.6608675032378253</v>
       </c>
       <c r="P2">
-        <v>1.07405140668518</v>
+        <v>-0.1638780530671466</v>
       </c>
       <c r="Q2">
-        <v>1.16817957659875</v>
+        <v>0.6098915818924954</v>
       </c>
       <c r="R2">
-        <v>1.2497282163627</v>
+        <v>1.652039356129778</v>
       </c>
       <c r="S2">
-        <v>1.30594839748726</v>
+        <v>2.306381313737713</v>
       </c>
       <c r="T2">
-        <v>1.35309242714172</v>
+        <v>2.807212147136925</v>
       </c>
     </row>
     <row r="3">
@@ -7838,23 +9777,23 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spatial</t>
+          <t>NoSpatial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>elev + slope</t>
         </is>
       </c>
       <c r="E3">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0.08599999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7862,37 +9801,43 @@
         </is>
       </c>
       <c r="H3">
-        <v>-0.378595736814313</v>
+        <v>-0.4620453404196815</v>
+      </c>
+      <c r="I3">
+        <v>0.2545835225975315</v>
+      </c>
+      <c r="J3">
+        <v>0.01902824749432508</v>
       </c>
       <c r="K3">
-        <v>-0.378595736814313</v>
+        <v>-0.4627417766160928</v>
       </c>
       <c r="L3">
-        <v>-0.644264936586549</v>
+        <v>-0.7303429406133702</v>
       </c>
       <c r="M3">
-        <v>-0.60699754266673</v>
+        <v>-0.6794998755070428</v>
       </c>
       <c r="N3">
-        <v>-0.5572711229510811</v>
+        <v>-0.6261253583693585</v>
       </c>
       <c r="O3">
-        <v>-0.469002699946436</v>
+        <v>-0.5457208057008913</v>
       </c>
       <c r="P3">
-        <v>-0.378595736814313</v>
+        <v>-0.4627417766160928</v>
       </c>
       <c r="Q3">
-        <v>-0.276341834639719</v>
+        <v>-0.3857074056069053</v>
       </c>
       <c r="R3">
-        <v>-0.192872504107463</v>
+        <v>-0.317289265376509</v>
       </c>
       <c r="S3">
-        <v>-0.139376447847833</v>
+        <v>-0.2765012150572836</v>
       </c>
       <c r="T3">
-        <v>-0.0942828409714854</v>
+        <v>-0.2328814161841863</v>
       </c>
     </row>
     <row r="4">
@@ -7902,8 +9847,1310 @@
         </is>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0.23</v>
+      </c>
+      <c r="F4">
+        <v>0.186</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>-0.4641479442825229</v>
+      </c>
+      <c r="I4">
+        <v>0.1337914400970451</v>
+      </c>
+      <c r="J4">
+        <v>0.005083105677329323</v>
+      </c>
+      <c r="K4">
+        <v>-0.4629818712561807</v>
+      </c>
+      <c r="L4">
+        <v>-0.7050612794147431</v>
+      </c>
+      <c r="M4">
+        <v>-0.663116549172501</v>
+      </c>
+      <c r="N4">
+        <v>-0.6183649119162893</v>
+      </c>
+      <c r="O4">
+        <v>-0.5440656514672902</v>
+      </c>
+      <c r="P4">
+        <v>-0.4629818712561807</v>
+      </c>
+      <c r="Q4">
+        <v>-0.3813302073263657</v>
+      </c>
+      <c r="R4">
+        <v>-0.3071454703408011</v>
+      </c>
+      <c r="S4">
+        <v>-0.2576345069383791</v>
+      </c>
+      <c r="T4">
+        <v>-0.219037243406177</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.162</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>beta_dist_str</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>0.04231658722215414</v>
+      </c>
+      <c r="I5">
+        <v>1.39416752281747</v>
+      </c>
+      <c r="J5">
+        <v>0.01760588539611647</v>
+      </c>
+      <c r="K5">
+        <v>0.102370817306454</v>
+      </c>
+      <c r="L5">
+        <v>-2.769083381781887</v>
+      </c>
+      <c r="M5">
+        <v>-2.34148459770346</v>
+      </c>
+      <c r="N5">
+        <v>-1.754833328554603</v>
+      </c>
+      <c r="O5">
+        <v>-0.8236609665773931</v>
+      </c>
+      <c r="P5">
+        <v>0.102370817306454</v>
+      </c>
+      <c r="Q5">
+        <v>0.8456913509998593</v>
+      </c>
+      <c r="R5">
+        <v>1.831407471918897</v>
+      </c>
+      <c r="S5">
+        <v>2.369498202926786</v>
+      </c>
+      <c r="T5">
+        <v>2.880130954478207</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.162</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>beta_elev</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>-0.05322354799165274</v>
+      </c>
+      <c r="I6">
+        <v>1.259278167990383</v>
+      </c>
+      <c r="J6">
+        <v>0.0184648995965419</v>
+      </c>
+      <c r="K6">
+        <v>-0.1905124957029205</v>
+      </c>
+      <c r="L6">
+        <v>-2.63108652468539</v>
+      </c>
+      <c r="M6">
+        <v>-2.144392360643442</v>
+      </c>
+      <c r="N6">
+        <v>-1.547796984145929</v>
+      </c>
+      <c r="O6">
+        <v>-0.5571034844798201</v>
+      </c>
+      <c r="P6">
+        <v>-0.1905124957029205</v>
+      </c>
+      <c r="Q6">
+        <v>0.5692175374369921</v>
+      </c>
+      <c r="R6">
+        <v>1.61907388982158</v>
+      </c>
+      <c r="S6">
+        <v>2.237659017169348</v>
+      </c>
+      <c r="T6">
+        <v>2.710765486804414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.162</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>-0.4821605191000704</v>
+      </c>
+      <c r="I7">
+        <v>0.2115816286257022</v>
+      </c>
+      <c r="J7">
+        <v>0.01863794156541684</v>
+      </c>
+      <c r="K7">
+        <v>-0.4672864559772039</v>
+      </c>
+      <c r="L7">
+        <v>-0.7297814701663312</v>
+      </c>
+      <c r="M7">
+        <v>-0.6783163678221694</v>
+      </c>
+      <c r="N7">
+        <v>-0.6302464282499047</v>
+      </c>
+      <c r="O7">
+        <v>-0.5519244356055517</v>
+      </c>
+      <c r="P7">
+        <v>-0.4672864559772039</v>
+      </c>
+      <c r="Q7">
+        <v>-0.3833053496120783</v>
+      </c>
+      <c r="R7">
+        <v>-0.3124795855062717</v>
+      </c>
+      <c r="S7">
+        <v>-0.2654350662298706</v>
+      </c>
+      <c r="T7">
+        <v>-0.2307745050005367</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope + BB</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0.82</v>
+      </c>
+      <c r="F8">
+        <v>0.138</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>beta_dist_str</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>0.01036914889033713</v>
+      </c>
+      <c r="I8">
+        <v>1.404564076109158</v>
+      </c>
+      <c r="J8">
+        <v>0.01788740999307633</v>
+      </c>
+      <c r="K8">
+        <v>0.05167792715745883</v>
+      </c>
+      <c r="L8">
+        <v>-2.815494712852236</v>
+      </c>
+      <c r="M8">
+        <v>-2.333132680200571</v>
+      </c>
+      <c r="N8">
+        <v>-1.82715654949084</v>
+      </c>
+      <c r="O8">
+        <v>-0.8725261599598371</v>
+      </c>
+      <c r="P8">
+        <v>0.05167792715745883</v>
+      </c>
+      <c r="Q8">
+        <v>0.836432384344674</v>
+      </c>
+      <c r="R8">
+        <v>1.830998066756566</v>
+      </c>
+      <c r="S8">
+        <v>2.395247074261397</v>
+      </c>
+      <c r="T8">
+        <v>2.875526487378172</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope + BB</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>0.82</v>
+      </c>
+      <c r="F9">
+        <v>0.138</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>beta_elev</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>-0.06732394061969775</v>
+      </c>
+      <c r="I9">
+        <v>1.319123215964547</v>
+      </c>
+      <c r="J9">
+        <v>0.018293203543272</v>
+      </c>
+      <c r="K9">
+        <v>-0.1704197531677483</v>
+      </c>
+      <c r="L9">
+        <v>-2.809016821762637</v>
+      </c>
+      <c r="M9">
+        <v>-2.344945128023159</v>
+      </c>
+      <c r="N9">
+        <v>-1.734269326128276</v>
+      </c>
+      <c r="O9">
+        <v>-0.6259941389785069</v>
+      </c>
+      <c r="P9">
+        <v>-0.1704197531677483</v>
+      </c>
+      <c r="Q9">
+        <v>0.6259215133103209</v>
+      </c>
+      <c r="R9">
+        <v>1.669597923412479</v>
+      </c>
+      <c r="S9">
+        <v>2.285179149496728</v>
+      </c>
+      <c r="T9">
+        <v>2.759980584962631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope + BB</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>0.82</v>
+      </c>
+      <c r="F10">
+        <v>0.138</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>-0.4794750317583447</v>
+      </c>
+      <c r="I10">
+        <v>0.1425818452388743</v>
+      </c>
+      <c r="J10">
+        <v>0.007280694400393682</v>
+      </c>
+      <c r="K10">
+        <v>-0.4752907247058064</v>
+      </c>
+      <c r="L10">
+        <v>-0.7351348770784424</v>
+      </c>
+      <c r="M10">
+        <v>-0.6798829815533174</v>
+      </c>
+      <c r="N10">
+        <v>-0.6341310951075825</v>
+      </c>
+      <c r="O10">
+        <v>-0.5559341318978385</v>
+      </c>
+      <c r="P10">
+        <v>-0.4752907247058064</v>
+      </c>
+      <c r="Q10">
+        <v>-0.3917355366253205</v>
+      </c>
+      <c r="R10">
+        <v>-0.3194652903651372</v>
+      </c>
+      <c r="S10">
+        <v>-0.2738857140979759</v>
+      </c>
+      <c r="T10">
+        <v>-0.2344341702019433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dist_str + elev + slope + BB</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>0.82</v>
+      </c>
+      <c r="F11">
+        <v>0.138</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>-0.05088454988882122</v>
+      </c>
+      <c r="I11">
+        <v>1.386112592448698</v>
+      </c>
+      <c r="J11">
+        <v>0.02214943011304592</v>
+      </c>
+      <c r="K11">
+        <v>0.02542884579505045</v>
+      </c>
+      <c r="L11">
+        <v>-2.858297110022291</v>
+      </c>
+      <c r="M11">
+        <v>-2.353512228550074</v>
+      </c>
+      <c r="N11">
+        <v>-1.814557209520452</v>
+      </c>
+      <c r="O11">
+        <v>-0.9128631067214185</v>
+      </c>
+      <c r="P11">
+        <v>0.02542884579505045</v>
+      </c>
+      <c r="Q11">
+        <v>0.7249835385328802</v>
+      </c>
+      <c r="R11">
+        <v>1.719230289369014</v>
+      </c>
+      <c r="S11">
+        <v>2.33617741645584</v>
+      </c>
+      <c r="T11">
+        <v>2.81406876044557</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>slope + DE</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.13</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>-0.4615748200550503</v>
+      </c>
+      <c r="I12">
+        <v>0.1261112536780309</v>
+      </c>
+      <c r="J12">
+        <v>0.004299103327344304</v>
+      </c>
+      <c r="K12">
+        <v>-0.4634950397947061</v>
+      </c>
+      <c r="L12">
+        <v>-0.7096801342698165</v>
+      </c>
+      <c r="M12">
+        <v>-0.666361111563525</v>
+      </c>
+      <c r="N12">
+        <v>-0.6204298367069817</v>
+      </c>
+      <c r="O12">
+        <v>-0.5461778340707911</v>
+      </c>
+      <c r="P12">
+        <v>-0.4634950397947061</v>
+      </c>
+      <c r="Q12">
+        <v>-0.3785126758118824</v>
+      </c>
+      <c r="R12">
+        <v>-0.3015444885870587</v>
+      </c>
+      <c r="S12">
+        <v>-0.2573942806043321</v>
+      </c>
+      <c r="T12">
+        <v>-0.2174152981839113</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>slope + DE</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.13</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>beta_DE</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>-0.06094676626529596</v>
+      </c>
+      <c r="I13">
+        <v>1.356230679171389</v>
+      </c>
+      <c r="J13">
+        <v>0.01734071867631386</v>
+      </c>
+      <c r="K13">
+        <v>-0.1526651941773805</v>
+      </c>
+      <c r="L13">
+        <v>-2.824951133313192</v>
+      </c>
+      <c r="M13">
+        <v>-2.335341195508677</v>
+      </c>
+      <c r="N13">
+        <v>-1.773776177152041</v>
+      </c>
+      <c r="O13">
+        <v>-0.7699343532481444</v>
+      </c>
+      <c r="P13">
+        <v>-0.1526651941773805</v>
+      </c>
+      <c r="Q13">
+        <v>0.7131014793856458</v>
+      </c>
+      <c r="R13">
+        <v>1.725629829064253</v>
+      </c>
+      <c r="S13">
+        <v>2.3121396561706</v>
+      </c>
+      <c r="T13">
+        <v>2.772906406515366</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ndvi_cv + slope</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>1.67</v>
+      </c>
+      <c r="F14">
+        <v>0.09</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>beta_ndvi_cv</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>-0.01487893447078034</v>
+      </c>
+      <c r="I14">
+        <v>1.449613695752614</v>
+      </c>
+      <c r="J14">
+        <v>0.01798237034759213</v>
+      </c>
+      <c r="K14">
+        <v>0.02707702394709099</v>
+      </c>
+      <c r="L14">
+        <v>-2.860761058557257</v>
+      </c>
+      <c r="M14">
+        <v>-2.39267422575917</v>
+      </c>
+      <c r="N14">
+        <v>-1.883528414755468</v>
+      </c>
+      <c r="O14">
+        <v>-0.9476020842083177</v>
+      </c>
+      <c r="P14">
+        <v>0.02707702394709099</v>
+      </c>
+      <c r="Q14">
+        <v>0.8968350919693733</v>
+      </c>
+      <c r="R14">
+        <v>1.873946747209562</v>
+      </c>
+      <c r="S14">
+        <v>2.422589707661751</v>
+      </c>
+      <c r="T14">
+        <v>2.89169479362201</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NoSpatial</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ndvi_cv + slope</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>1.67</v>
+      </c>
+      <c r="F15">
+        <v>0.09</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>-0.4703080365246954</v>
+      </c>
+      <c r="I15">
+        <v>0.1192603201601333</v>
+      </c>
+      <c r="J15">
+        <v>0.003902463066487625</v>
+      </c>
+      <c r="K15">
+        <v>-0.469194189098487</v>
+      </c>
+      <c r="L15">
+        <v>-0.7003034279930308</v>
+      </c>
+      <c r="M15">
+        <v>-0.6652088579201505</v>
+      </c>
+      <c r="N15">
+        <v>-0.6227351157980305</v>
+      </c>
+      <c r="O15">
+        <v>-0.5515770752424153</v>
+      </c>
+      <c r="P15">
+        <v>-0.469194189098487</v>
+      </c>
+      <c r="Q15">
+        <v>-0.3902228094884012</v>
+      </c>
+      <c r="R15">
+        <v>-0.3187429664989092</v>
+      </c>
+      <c r="S15">
+        <v>-0.277403969123182</v>
+      </c>
+      <c r="T15">
+        <v>-0.2393618681648919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>slope + DE</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>1.78</v>
+      </c>
+      <c r="F16">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H16">
+        <v>0.9913246815817253</v>
+      </c>
+      <c r="I16">
+        <v>0.1486425865056107</v>
+      </c>
+      <c r="J16">
+        <v>0.07213722008225137</v>
+      </c>
+      <c r="K16">
+        <v>0.9878755523844958</v>
+      </c>
+      <c r="L16">
+        <v>0.7279944877166254</v>
+      </c>
+      <c r="M16">
+        <v>0.7371188449482147</v>
+      </c>
+      <c r="N16">
+        <v>0.7743181150038695</v>
+      </c>
+      <c r="O16">
+        <v>0.8619205289881153</v>
+      </c>
+      <c r="P16">
+        <v>0.9878755523844958</v>
+      </c>
+      <c r="Q16">
+        <v>1.117927317454629</v>
+      </c>
+      <c r="R16">
+        <v>1.16541726466529</v>
+      </c>
+      <c r="S16">
+        <v>1.187348662974869</v>
+      </c>
+      <c r="T16">
+        <v>1.238820953748188</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>slope + DE</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>1.78</v>
+      </c>
+      <c r="F17">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H17">
+        <v>-0.3838608964561235</v>
+      </c>
+      <c r="I17">
+        <v>0.1465721466766946</v>
+      </c>
+      <c r="J17">
+        <v>0.05303669350570862</v>
+      </c>
+      <c r="K17">
+        <v>-0.3832811766334352</v>
+      </c>
+      <c r="L17">
+        <v>-0.6370263417604732</v>
+      </c>
+      <c r="M17">
+        <v>-0.6352017157346311</v>
+      </c>
+      <c r="N17">
+        <v>-0.5991325373380201</v>
+      </c>
+      <c r="O17">
+        <v>-0.4907754903044245</v>
+      </c>
+      <c r="P17">
+        <v>-0.3832811766334352</v>
+      </c>
+      <c r="Q17">
+        <v>-0.2714155725936253</v>
+      </c>
+      <c r="R17">
+        <v>-0.1890848368035216</v>
+      </c>
+      <c r="S17">
+        <v>-0.1761133258253265</v>
+      </c>
+      <c r="T17">
+        <v>-0.1587382419982914</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Muntjac</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>slope + DE</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>1.78</v>
+      </c>
+      <c r="F18">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>beta_DE</t>
+        </is>
+      </c>
+      <c r="H18">
+        <v>-0.1931206743608491</v>
+      </c>
+      <c r="I18">
+        <v>0.09717644539779957</v>
+      </c>
+      <c r="J18">
+        <v>0.01264439576963174</v>
+      </c>
+      <c r="K18">
+        <v>-0.1910095792674409</v>
+      </c>
+      <c r="L18">
+        <v>-0.3750590435853822</v>
+      </c>
+      <c r="M18">
+        <v>-0.3393807437646424</v>
+      </c>
+      <c r="N18">
+        <v>-0.3181927035743626</v>
+      </c>
+      <c r="O18">
+        <v>-0.2616662465359703</v>
+      </c>
+      <c r="P18">
+        <v>-0.1910095792674409</v>
+      </c>
+      <c r="Q18">
+        <v>-0.1203834756936969</v>
+      </c>
+      <c r="R18">
+        <v>-0.0748755040922944</v>
+      </c>
+      <c r="S18">
+        <v>-0.03198693983440308</v>
+      </c>
+      <c r="T18">
+        <v>-0.01161898846837328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Model_Covariates</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta_wAIC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MCSE</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>q2.5%</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>q5%</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>q10%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>q25%</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>q50%</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>q75%</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>q90%</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>q95%</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>q97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.527</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>beta0 (Intercept)</t>
+        </is>
+      </c>
+      <c r="H2">
+        <v>0.05054202369146823</v>
+      </c>
+      <c r="I2">
+        <v>0.18293473449882</v>
+      </c>
+      <c r="J2">
+        <v>0.02973638249281557</v>
+      </c>
+      <c r="K2">
+        <v>0.06849731900321554</v>
+      </c>
+      <c r="L2">
+        <v>-0.3392071389383966</v>
+      </c>
+      <c r="M2">
+        <v>-0.3277277151963257</v>
+      </c>
+      <c r="N2">
+        <v>-0.1980056925305528</v>
+      </c>
+      <c r="O2">
+        <v>-0.06215808876269596</v>
+      </c>
+      <c r="P2">
+        <v>0.06849731900321554</v>
+      </c>
+      <c r="Q2">
+        <v>0.179236479877801</v>
+      </c>
+      <c r="R2">
+        <v>0.271673311941279</v>
+      </c>
+      <c r="S2">
+        <v>0.3404629553279683</v>
+      </c>
+      <c r="T2">
+        <v>0.3765036166037736</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0.527</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>0.4755651908038078</v>
+      </c>
+      <c r="I3">
+        <v>0.2002705337387587</v>
+      </c>
+      <c r="J3">
+        <v>0.0271018785245539</v>
+      </c>
+      <c r="K3">
+        <v>0.4995359809654409</v>
+      </c>
+      <c r="L3">
+        <v>0.09784859383797573</v>
+      </c>
+      <c r="M3">
+        <v>0.1110114021830484</v>
+      </c>
+      <c r="N3">
+        <v>0.1641154136389191</v>
+      </c>
+      <c r="O3">
+        <v>0.3494439742191254</v>
+      </c>
+      <c r="P3">
+        <v>0.4995359809654409</v>
+      </c>
+      <c r="Q3">
+        <v>0.6323846662815329</v>
+      </c>
+      <c r="R3">
+        <v>0.7170164003171264</v>
+      </c>
+      <c r="S3">
+        <v>0.7788188954757386</v>
+      </c>
+      <c r="T3">
+        <v>0.7976733698878778</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Spatial</t>
@@ -7911,52 +11158,198 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>slope + DE</t>
+          <t>slope + BB</t>
         </is>
       </c>
       <c r="E4">
-        <v>1.78</v>
+        <v>0.68</v>
       </c>
       <c r="F4">
-        <v>0.08599999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>beta_DE</t>
+          <t>beta0 (Intercept)</t>
         </is>
       </c>
       <c r="H4">
-        <v>-0.177221471563296</v>
+        <v>-0.1700574849594609</v>
+      </c>
+      <c r="I4">
+        <v>0.236909529928073</v>
+      </c>
+      <c r="J4">
+        <v>0.0485347774459452</v>
       </c>
       <c r="K4">
-        <v>-0.177221471563296</v>
+        <v>-0.1339026613417365</v>
       </c>
       <c r="L4">
-        <v>-0.49692814622282</v>
+        <v>-0.589878074973992</v>
       </c>
       <c r="M4">
-        <v>-0.435774592429638</v>
+        <v>-0.589878074973992</v>
       </c>
       <c r="N4">
-        <v>-0.380767144712005</v>
+        <v>-0.5081418554541016</v>
       </c>
       <c r="O4">
-        <v>-0.28293251345545</v>
+        <v>-0.3336773859602196</v>
       </c>
       <c r="P4">
-        <v>-0.177221471563296</v>
+        <v>-0.1339026613417365</v>
       </c>
       <c r="Q4">
-        <v>-0.0845198490070406</v>
+        <v>-0.006045483630314619</v>
       </c>
       <c r="R4">
-        <v>-0.00852748603690923</v>
+        <v>0.1590902455516887</v>
       </c>
       <c r="S4">
-        <v>0.0339845847206532</v>
+        <v>0.2084246284477436</v>
       </c>
       <c r="T4">
-        <v>0.0750051337890095</v>
+        <v>0.2693941014419244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>slope + BB</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.68</v>
+      </c>
+      <c r="F5">
+        <v>0.375</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>beta_slope</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>0.5093603968579351</v>
+      </c>
+      <c r="I5">
+        <v>0.2174998294134232</v>
+      </c>
+      <c r="J5">
+        <v>0.02538998049761626</v>
+      </c>
+      <c r="K5">
+        <v>0.5056210538686133</v>
+      </c>
+      <c r="L5">
+        <v>0.1436298659645323</v>
+      </c>
+      <c r="M5">
+        <v>0.1563675527661607</v>
+      </c>
+      <c r="N5">
+        <v>0.2303302454865548</v>
+      </c>
+      <c r="O5">
+        <v>0.3749350277917692</v>
+      </c>
+      <c r="P5">
+        <v>0.5056210538686133</v>
+      </c>
+      <c r="Q5">
+        <v>0.6484994494239853</v>
+      </c>
+      <c r="R5">
+        <v>0.7709436728222155</v>
+      </c>
+      <c r="S5">
+        <v>0.8604448264521787</v>
+      </c>
+      <c r="T5">
+        <v>0.9888076830100602</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wild boar</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Spatial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>slope + BB</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0.68</v>
+      </c>
+      <c r="F6">
+        <v>0.375</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>beta_BB</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>-1.266277759603915</v>
+      </c>
+      <c r="I6">
+        <v>0.8346447652605108</v>
+      </c>
+      <c r="J6">
+        <v>0.1606176425928626</v>
+      </c>
+      <c r="K6">
+        <v>-1.23201575320496</v>
+      </c>
+      <c r="L6">
+        <v>-2.840720392377818</v>
+      </c>
+      <c r="M6">
+        <v>-2.76987698365658</v>
+      </c>
+      <c r="N6">
+        <v>-2.431118794959679</v>
+      </c>
+      <c r="O6">
+        <v>-1.8369517251953</v>
+      </c>
+      <c r="P6">
+        <v>-1.23201575320496</v>
+      </c>
+      <c r="Q6">
+        <v>-0.6271849377994259</v>
+      </c>
+      <c r="R6">
+        <v>-0.2328525694455612</v>
+      </c>
+      <c r="S6">
+        <v>0.05194658859315354</v>
+      </c>
+      <c r="T6">
+        <v>0.1028185801768376</v>
       </c>
     </row>
   </sheetData>

--- a/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
+++ b/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
@@ -1062,43 +1062,43 @@
         </is>
       </c>
       <c r="C14">
-        <v>4.399524082903509</v>
+        <v>4.410839548191006</v>
       </c>
       <c r="D14">
-        <v>0.4515033947672068</v>
+        <v>0.467828769273879</v>
       </c>
       <c r="E14">
-        <v>0.01703103072752752</v>
+        <v>0.01130454264506064</v>
       </c>
       <c r="F14">
-        <v>4.369848808483351</v>
+        <v>4.373566168925842</v>
       </c>
       <c r="G14">
-        <v>3.619223080911201</v>
+        <v>3.596753068911467</v>
       </c>
       <c r="H14">
-        <v>3.725703299932598</v>
+        <v>3.707836193317775</v>
       </c>
       <c r="I14">
-        <v>3.856692583835749</v>
+        <v>3.845175006675777</v>
       </c>
       <c r="J14">
-        <v>4.084344492600104</v>
+        <v>4.084204196605862</v>
       </c>
       <c r="K14">
-        <v>4.369848808483351</v>
+        <v>4.373566168925842</v>
       </c>
       <c r="L14">
-        <v>4.66913632128504</v>
+        <v>4.696162248635995</v>
       </c>
       <c r="M14">
-        <v>4.978525010525605</v>
+        <v>5.033857068034441</v>
       </c>
       <c r="N14">
-        <v>5.198957201935871</v>
+        <v>5.24194276694994</v>
       </c>
       <c r="O14">
-        <v>5.392367958147705</v>
+        <v>5.430085206221917</v>
       </c>
     </row>
     <row r="15">
@@ -1113,43 +1113,43 @@
         </is>
       </c>
       <c r="C15">
-        <v>13246.96701362246</v>
+        <v>13281.03787960312</v>
       </c>
       <c r="D15">
-        <v>1359.47672164406</v>
+        <v>1408.63242428365</v>
       </c>
       <c r="E15">
-        <v>51.28043352058523</v>
+        <v>34.03797790427834</v>
       </c>
       <c r="F15">
-        <v>13157.61476234337</v>
+        <v>13168.80773463571</v>
       </c>
       <c r="G15">
-        <v>10897.48069662363</v>
+        <v>10829.82349049243</v>
       </c>
       <c r="H15">
-        <v>11218.09263609705</v>
+        <v>11164.29477807982</v>
       </c>
       <c r="I15">
-        <v>11612.50136992944</v>
+        <v>11577.82194510076</v>
       </c>
       <c r="J15">
-        <v>12297.96126721891</v>
+        <v>12297.53883598025</v>
       </c>
       <c r="K15">
-        <v>13157.61476234337</v>
+        <v>13168.80773463571</v>
       </c>
       <c r="L15">
-        <v>14058.76946338926</v>
+        <v>14140.14453064298</v>
       </c>
       <c r="M15">
-        <v>14990.33880669259</v>
+        <v>15156.9436318517</v>
       </c>
       <c r="N15">
-        <v>15654.06013502891</v>
+        <v>15783.48967128627</v>
       </c>
       <c r="O15">
-        <v>16236.41992198274</v>
+        <v>16349.98655593419</v>
       </c>
     </row>
     <row r="16">
@@ -1164,43 +1164,43 @@
         </is>
       </c>
       <c r="C16">
-        <v>4.678647967317327</v>
+        <v>4.690681332215209</v>
       </c>
       <c r="D16">
-        <v>0.4801486252509269</v>
+        <v>0.4975097485933698</v>
       </c>
       <c r="E16">
-        <v>0.01811154929332223</v>
+        <v>0.01202174927813127</v>
       </c>
       <c r="F16">
-        <v>4.647089971559334</v>
+        <v>4.651043176622045</v>
       </c>
       <c r="G16">
-        <v>3.848841463688045</v>
+        <v>3.824945861803132</v>
       </c>
       <c r="H16">
-        <v>3.962077225305965</v>
+        <v>3.943076556035821</v>
       </c>
       <c r="I16">
-        <v>4.101377007583637</v>
+        <v>4.089128708005659</v>
       </c>
       <c r="J16">
-        <v>4.343472088807363</v>
+        <v>4.343322891858802</v>
       </c>
       <c r="K16">
-        <v>4.647089971559334</v>
+        <v>4.651043176622045</v>
       </c>
       <c r="L16">
-        <v>4.965365513874121</v>
+        <v>4.994106077099305</v>
       </c>
       <c r="M16">
-        <v>5.294383092764388</v>
+        <v>5.353225643347804</v>
       </c>
       <c r="N16">
-        <v>5.528800408100988</v>
+        <v>5.574513153976976</v>
       </c>
       <c r="O16">
-        <v>5.734481937365534</v>
+        <v>5.774592122628746</v>
       </c>
     </row>
     <row r="17">
@@ -1215,43 +1215,43 @@
         </is>
       </c>
       <c r="C17">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="D17">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="E17">
-        <v>54.53387492219304</v>
+        <v>36.19748707645297</v>
       </c>
       <c r="F17">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="G17">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="H17">
-        <v>11929.81452539626</v>
+        <v>11872.60351022386</v>
       </c>
       <c r="I17">
-        <v>12349.24616983433</v>
+        <v>12312.36653980504</v>
       </c>
       <c r="J17">
-        <v>13078.19445939897</v>
+        <v>13077.74522738685</v>
       </c>
       <c r="K17">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="L17">
-        <v>14950.71556227498</v>
+        <v>15037.25339814601</v>
       </c>
       <c r="M17">
-        <v>15941.38749231357</v>
+        <v>16118.56241212024</v>
       </c>
       <c r="N17">
-        <v>16647.21802879207</v>
+        <v>16784.85910662467</v>
       </c>
       <c r="O17">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
     </row>
     <row r="18">
@@ -4261,43 +4261,43 @@
         </is>
       </c>
       <c r="H40">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I40">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J40">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K40">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L40">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M40">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N40">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O40">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P40">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q40">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R40">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S40">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T40">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="41">
@@ -4331,43 +4331,43 @@
         </is>
       </c>
       <c r="H41">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I41">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J41">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K41">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L41">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M41">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N41">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O41">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P41">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q41">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R41">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S41">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T41">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="42">
@@ -4401,43 +4401,43 @@
         </is>
       </c>
       <c r="H42">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I42">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J42">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K42">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L42">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M42">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N42">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O42">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P42">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q42">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R42">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S42">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T42">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="43">
@@ -4471,43 +4471,43 @@
         </is>
       </c>
       <c r="H43">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I43">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J43">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K43">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L43">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M43">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N43">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O43">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P43">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q43">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R43">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S43">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T43">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="44">
@@ -4541,43 +4541,43 @@
         </is>
       </c>
       <c r="H44">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I44">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J44">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K44">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L44">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M44">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N44">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O44">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P44">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q44">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R44">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S44">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T44">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="45">
@@ -4611,43 +4611,43 @@
         </is>
       </c>
       <c r="H45">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I45">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J45">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K45">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L45">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M45">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N45">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O45">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P45">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q45">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R45">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S45">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T45">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="46">
@@ -4681,43 +4681,43 @@
         </is>
       </c>
       <c r="H46">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="I46">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="J46">
-        <v>0.007443507277702275</v>
+        <v>0.005740520804359723</v>
       </c>
       <c r="K46">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="L46">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="M46">
-        <v>0.07529715532475259</v>
+        <v>0.07728212611721173</v>
       </c>
       <c r="N46">
-        <v>0.1330345569714191</v>
+        <v>0.1379085124364979</v>
       </c>
       <c r="O46">
-        <v>0.2230796353816032</v>
+        <v>0.2323905509752022</v>
       </c>
       <c r="P46">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="Q46">
-        <v>0.4062321658569829</v>
+        <v>0.4212820878663344</v>
       </c>
       <c r="R46">
-        <v>0.4797921499961845</v>
+        <v>0.4998753731485056</v>
       </c>
       <c r="S46">
-        <v>0.5273055052693616</v>
+        <v>0.5460390596689056</v>
       </c>
       <c r="T46">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
     </row>
     <row r="47">
@@ -4751,43 +4751,43 @@
         </is>
       </c>
       <c r="H47">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I47">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J47">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K47">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L47">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M47">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N47">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O47">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P47">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q47">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R47">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S47">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T47">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="48">
@@ -4821,43 +4821,43 @@
         </is>
       </c>
       <c r="H48">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I48">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J48">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K48">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L48">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M48">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N48">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O48">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P48">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q48">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R48">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S48">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T48">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="49">
@@ -4891,43 +4891,43 @@
         </is>
       </c>
       <c r="H49">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I49">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J49">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K49">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L49">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M49">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N49">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O49">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P49">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q49">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R49">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S49">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T49">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="50">
@@ -4961,43 +4961,43 @@
         </is>
       </c>
       <c r="H50">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="I50">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="J50">
-        <v>0.007443507277702275</v>
+        <v>0.005740520804359723</v>
       </c>
       <c r="K50">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="L50">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="M50">
-        <v>0.07529715532475259</v>
+        <v>0.07728212611721173</v>
       </c>
       <c r="N50">
-        <v>0.1330345569714191</v>
+        <v>0.1379085124364979</v>
       </c>
       <c r="O50">
-        <v>0.2230796353816032</v>
+        <v>0.2323905509752022</v>
       </c>
       <c r="P50">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="Q50">
-        <v>0.4062321658569829</v>
+        <v>0.4212820878663344</v>
       </c>
       <c r="R50">
-        <v>0.4797921499961845</v>
+        <v>0.4998753731485056</v>
       </c>
       <c r="S50">
-        <v>0.5273055052693616</v>
+        <v>0.5460390596689056</v>
       </c>
       <c r="T50">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
     </row>
     <row r="51">
@@ -5031,43 +5031,43 @@
         </is>
       </c>
       <c r="H51">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I51">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J51">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K51">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L51">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M51">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N51">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O51">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P51">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q51">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R51">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S51">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T51">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="52">
@@ -5101,43 +5101,43 @@
         </is>
       </c>
       <c r="H52">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I52">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J52">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K52">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L52">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M52">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N52">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O52">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P52">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q52">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R52">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S52">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T52">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="53">
@@ -5171,43 +5171,43 @@
         </is>
       </c>
       <c r="H53">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="I53">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="J53">
-        <v>0.1084019016706564</v>
+        <v>0.07701312410586839</v>
       </c>
       <c r="K53">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="L53">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="M53">
-        <v>-3.488032961964862</v>
+        <v>-3.387966630833503</v>
       </c>
       <c r="N53">
-        <v>-3.003823218096905</v>
+        <v>-2.975243907002977</v>
       </c>
       <c r="O53">
-        <v>-2.290316942476073</v>
+        <v>-2.349070501240922</v>
       </c>
       <c r="P53">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="Q53">
-        <v>-0.9999871789526356</v>
+        <v>-0.9754761953429016</v>
       </c>
       <c r="R53">
-        <v>-0.2572257762999619</v>
+        <v>-0.183671580782594</v>
       </c>
       <c r="S53">
-        <v>0.03687330688384052</v>
+        <v>0.04702015061722756</v>
       </c>
       <c r="T53">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
     </row>
     <row r="54">
@@ -5241,43 +5241,43 @@
         </is>
       </c>
       <c r="H54">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I54">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J54">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K54">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L54">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M54">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N54">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O54">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P54">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q54">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R54">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S54">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T54">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="55">
@@ -5311,43 +5311,43 @@
         </is>
       </c>
       <c r="H55">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I55">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J55">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K55">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L55">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M55">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N55">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O55">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P55">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q55">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R55">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S55">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T55">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="56">
@@ -5381,43 +5381,43 @@
         </is>
       </c>
       <c r="H56">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="I56">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="J56">
-        <v>0.004489188844228981</v>
+        <v>0.002401968778905081</v>
       </c>
       <c r="K56">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="L56">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="M56">
-        <v>-0.3311505668231341</v>
+        <v>-0.3207942158070026</v>
       </c>
       <c r="N56">
-        <v>-0.2733669922777434</v>
+        <v>-0.2750567385371742</v>
       </c>
       <c r="O56">
-        <v>-0.1881028706283962</v>
+        <v>-0.1909895861441369</v>
       </c>
       <c r="P56">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="Q56">
-        <v>-0.01150899139302317</v>
+        <v>-0.01958741750834391</v>
       </c>
       <c r="R56">
-        <v>0.05620358718629397</v>
+        <v>0.05288336647867456</v>
       </c>
       <c r="S56">
-        <v>0.09790972252884569</v>
+        <v>0.09529479881860209</v>
       </c>
       <c r="T56">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
     </row>
     <row r="57">
@@ -5451,43 +5451,43 @@
         </is>
       </c>
       <c r="H57">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I57">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J57">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K57">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L57">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M57">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N57">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O57">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P57">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q57">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R57">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S57">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T57">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="58">
@@ -5521,43 +5521,43 @@
         </is>
       </c>
       <c r="H58">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="I58">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="J58">
-        <v>0.00477873489985893</v>
+        <v>0.004006584006451343</v>
       </c>
       <c r="K58">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="L58">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="M58">
-        <v>-0.3046267419691921</v>
+        <v>-0.3268116841121991</v>
       </c>
       <c r="N58">
-        <v>-0.2621410833031751</v>
+        <v>-0.283057820858777</v>
       </c>
       <c r="O58">
-        <v>-0.1948690341940331</v>
+        <v>-0.2106015902179914</v>
       </c>
       <c r="P58">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="Q58">
-        <v>-0.04023992026320443</v>
+        <v>-0.04965583352737096</v>
       </c>
       <c r="R58">
-        <v>0.02516573387752361</v>
+        <v>0.025814225589536</v>
       </c>
       <c r="S58">
-        <v>0.0687494092616685</v>
+        <v>0.06749840563798652</v>
       </c>
       <c r="T58">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
     </row>
     <row r="59">
@@ -5591,43 +5591,43 @@
         </is>
       </c>
       <c r="H59">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I59">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J59">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K59">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L59">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M59">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N59">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O59">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P59">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q59">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R59">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S59">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T59">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="60">
@@ -5661,43 +5661,43 @@
         </is>
       </c>
       <c r="H60">
-        <v>0.9183909914910773</v>
+        <v>0.9350824013936898</v>
       </c>
       <c r="I60">
-        <v>0.1304830711675759</v>
+        <v>0.1287839575270144</v>
       </c>
       <c r="J60">
-        <v>0.007629190739139556</v>
+        <v>0.004911631260971691</v>
       </c>
       <c r="K60">
-        <v>0.9188769232333426</v>
+        <v>0.9339599256730006</v>
       </c>
       <c r="L60">
-        <v>0.6586142205919907</v>
+        <v>0.6837604478264198</v>
       </c>
       <c r="M60">
-        <v>0.6973144818432745</v>
+        <v>0.7256969263309898</v>
       </c>
       <c r="N60">
-        <v>0.7525626104506297</v>
+        <v>0.7721319863560734</v>
       </c>
       <c r="O60">
-        <v>0.835069406160258</v>
+        <v>0.8480878806056904</v>
       </c>
       <c r="P60">
-        <v>0.9188769232333426</v>
+        <v>0.9339599256730006</v>
       </c>
       <c r="Q60">
-        <v>1.006385161414666</v>
+        <v>1.022096874431145</v>
       </c>
       <c r="R60">
-        <v>1.083930819456203</v>
+        <v>1.09963839975358</v>
       </c>
       <c r="S60">
-        <v>1.134951693682448</v>
+        <v>1.149915295602883</v>
       </c>
       <c r="T60">
-        <v>1.172675806558851</v>
+        <v>1.188425484603933</v>
       </c>
     </row>
     <row r="61">
@@ -5731,43 +5731,43 @@
         </is>
       </c>
       <c r="H61">
-        <v>-0.4065596936517923</v>
+        <v>-0.3861219822456349</v>
       </c>
       <c r="I61">
-        <v>0.1367732975379721</v>
+        <v>0.1375031246846421</v>
       </c>
       <c r="J61">
-        <v>0.007752243424404085</v>
+        <v>0.005396993969338132</v>
       </c>
       <c r="K61">
-        <v>-0.4059009629105702</v>
+        <v>-0.3844796819927853</v>
       </c>
       <c r="L61">
-        <v>-0.6808653523379501</v>
+        <v>-0.660343584330276</v>
       </c>
       <c r="M61">
-        <v>-0.6290055510176999</v>
+        <v>-0.6127355638936063</v>
       </c>
       <c r="N61">
-        <v>-0.5826112935258686</v>
+        <v>-0.5631256427215817</v>
       </c>
       <c r="O61">
-        <v>-0.4980215224411933</v>
+        <v>-0.4774900201554068</v>
       </c>
       <c r="P61">
-        <v>-0.4059009629105702</v>
+        <v>-0.3844796819927853</v>
       </c>
       <c r="Q61">
-        <v>-0.3120138456327275</v>
+        <v>-0.2959074369696905</v>
       </c>
       <c r="R61">
-        <v>-0.2362582856643825</v>
+        <v>-0.2133831762162299</v>
       </c>
       <c r="S61">
-        <v>-0.1875672023811518</v>
+        <v>-0.1617123972455172</v>
       </c>
       <c r="T61">
-        <v>-0.13768853671991</v>
+        <v>-0.1103279673395892</v>
       </c>
     </row>
     <row r="62">
@@ -5801,43 +5801,43 @@
         </is>
       </c>
       <c r="H62">
-        <v>-0.1889578831058645</v>
+        <v>-0.1831147261014914</v>
       </c>
       <c r="I62">
-        <v>0.1327116504290296</v>
+        <v>0.1350369720875784</v>
       </c>
       <c r="J62">
-        <v>0.004988553944890132</v>
+        <v>0.003915876801680832</v>
       </c>
       <c r="K62">
-        <v>-0.1854118738502842</v>
+        <v>-0.1785893086645667</v>
       </c>
       <c r="L62">
-        <v>-0.4602265954673859</v>
+        <v>-0.4649684790586853</v>
       </c>
       <c r="M62">
-        <v>-0.4109149079112364</v>
+        <v>-0.4154883456029336</v>
       </c>
       <c r="N62">
-        <v>-0.3562558322924651</v>
+        <v>-0.358318296277535</v>
       </c>
       <c r="O62">
-        <v>-0.2767524515129072</v>
+        <v>-0.2698399395404846</v>
       </c>
       <c r="P62">
-        <v>-0.1854118738502842</v>
+        <v>-0.1785893086645667</v>
       </c>
       <c r="Q62">
-        <v>-0.09630601969289393</v>
+        <v>-0.09008199488237223</v>
       </c>
       <c r="R62">
-        <v>-0.02334182334123727</v>
+        <v>-0.01445770825028103</v>
       </c>
       <c r="S62">
-        <v>0.02185289638685428</v>
+        <v>0.03175994551138536</v>
       </c>
       <c r="T62">
-        <v>0.0567593032052706</v>
+        <v>0.06508679198580132</v>
       </c>
     </row>
     <row r="63">
@@ -5871,43 +5871,43 @@
         </is>
       </c>
       <c r="H63">
-        <v>0.4928832352681846</v>
+        <v>0.5216747421585012</v>
       </c>
       <c r="I63">
-        <v>0.2081492105235483</v>
+        <v>0.1656690180157772</v>
       </c>
       <c r="J63">
-        <v>0.142336995204372</v>
+        <v>0.06199340762075325</v>
       </c>
       <c r="K63">
-        <v>0.4948766498617353</v>
+        <v>0.4970093760277954</v>
       </c>
       <c r="L63">
-        <v>0.194505971157467</v>
+        <v>0.2544938193727065</v>
       </c>
       <c r="M63">
-        <v>0.214159402191094</v>
+        <v>0.2818463068147971</v>
       </c>
       <c r="N63">
-        <v>0.2338548175674627</v>
+        <v>0.3183431310005265</v>
       </c>
       <c r="O63">
-        <v>0.3454576614088294</v>
+        <v>0.4034339590777929</v>
       </c>
       <c r="P63">
-        <v>0.4948766498617353</v>
+        <v>0.4970093760277954</v>
       </c>
       <c r="Q63">
-        <v>0.5778643295666729</v>
+        <v>0.621124205496744</v>
       </c>
       <c r="R63">
-        <v>0.7787218439451356</v>
+        <v>0.7744348303172901</v>
       </c>
       <c r="S63">
-        <v>0.9380251412749596</v>
+        <v>0.8405695748132813</v>
       </c>
       <c r="T63">
-        <v>1.018700735436573</v>
+        <v>0.867919380982383</v>
       </c>
     </row>
     <row r="64">
@@ -7963,43 +7963,43 @@
         <v>1.06</v>
       </c>
       <c r="F5">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="G5">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="H5">
-        <v>0.0002271076041062111</v>
+        <v>0.0001464555606329597</v>
       </c>
       <c r="I5">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="J5">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="K5">
-        <v>1.58232864116933</v>
+        <v>1.582405565624905</v>
       </c>
       <c r="L5">
-        <v>1.582751154194213</v>
+        <v>1.582791209486076</v>
       </c>
       <c r="M5">
-        <v>1.584179616121803</v>
+        <v>1.584142124250705</v>
       </c>
       <c r="N5">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="O5">
-        <v>1.592126237203439</v>
+        <v>1.592257135192646</v>
       </c>
       <c r="P5">
-        <v>1.598731928006224</v>
+        <v>1.599159409399299</v>
       </c>
       <c r="Q5">
-        <v>1.603723493396287</v>
+        <v>1.604247882397833</v>
       </c>
       <c r="R5">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
     </row>
     <row r="6">
@@ -12461,43 +12461,43 @@
         </is>
       </c>
       <c r="H2">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I2">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J2">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K2">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L2">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M2">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N2">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O2">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P2">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q2">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R2">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S2">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T2">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="3">
@@ -12531,43 +12531,43 @@
         </is>
       </c>
       <c r="H3">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I3">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J3">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K3">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L3">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M3">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N3">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O3">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P3">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q3">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R3">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S3">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T3">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="4">
@@ -12601,43 +12601,43 @@
         </is>
       </c>
       <c r="H4">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I4">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J4">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K4">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L4">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M4">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N4">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O4">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P4">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q4">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R4">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S4">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T4">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="5">
@@ -12671,43 +12671,43 @@
         </is>
       </c>
       <c r="H5">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I5">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J5">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K5">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L5">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M5">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N5">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O5">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P5">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q5">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R5">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S5">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T5">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="6">
@@ -12741,43 +12741,43 @@
         </is>
       </c>
       <c r="H6">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I6">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J6">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K6">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L6">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M6">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N6">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O6">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P6">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q6">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R6">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S6">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T6">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="7">
@@ -12811,43 +12811,43 @@
         </is>
       </c>
       <c r="H7">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I7">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J7">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K7">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L7">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M7">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N7">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O7">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P7">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q7">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R7">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S7">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T7">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="8">
@@ -12881,43 +12881,43 @@
         </is>
       </c>
       <c r="H8">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="I8">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="J8">
-        <v>0.007443507277702275</v>
+        <v>0.005740520804359723</v>
       </c>
       <c r="K8">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="L8">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="M8">
-        <v>0.07529715532475259</v>
+        <v>0.07728212611721173</v>
       </c>
       <c r="N8">
-        <v>0.1330345569714191</v>
+        <v>0.1379085124364979</v>
       </c>
       <c r="O8">
-        <v>0.2230796353816032</v>
+        <v>0.2323905509752022</v>
       </c>
       <c r="P8">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="Q8">
-        <v>0.4062321658569829</v>
+        <v>0.4212820878663344</v>
       </c>
       <c r="R8">
-        <v>0.4797921499961845</v>
+        <v>0.4998753731485056</v>
       </c>
       <c r="S8">
-        <v>0.5273055052693616</v>
+        <v>0.5460390596689056</v>
       </c>
       <c r="T8">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
     </row>
     <row r="9">
@@ -12951,43 +12951,43 @@
         </is>
       </c>
       <c r="H9">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I9">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J9">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K9">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L9">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M9">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N9">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O9">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P9">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q9">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R9">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S9">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T9">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="10">
@@ -13021,43 +13021,43 @@
         </is>
       </c>
       <c r="H10">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I10">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J10">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K10">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L10">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M10">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N10">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O10">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P10">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q10">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R10">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S10">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T10">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="11">
@@ -13091,43 +13091,43 @@
         </is>
       </c>
       <c r="H11">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I11">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J11">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K11">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L11">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M11">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N11">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O11">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P11">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q11">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R11">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S11">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T11">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="12">
@@ -13161,43 +13161,43 @@
         </is>
       </c>
       <c r="H12">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="I12">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="J12">
-        <v>0.007443507277702275</v>
+        <v>0.005740520804359723</v>
       </c>
       <c r="K12">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="L12">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="M12">
-        <v>0.07529715532475259</v>
+        <v>0.07728212611721173</v>
       </c>
       <c r="N12">
-        <v>0.1330345569714191</v>
+        <v>0.1379085124364979</v>
       </c>
       <c r="O12">
-        <v>0.2230796353816032</v>
+        <v>0.2323905509752022</v>
       </c>
       <c r="P12">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="Q12">
-        <v>0.4062321658569829</v>
+        <v>0.4212820878663344</v>
       </c>
       <c r="R12">
-        <v>0.4797921499961845</v>
+        <v>0.4998753731485056</v>
       </c>
       <c r="S12">
-        <v>0.5273055052693616</v>
+        <v>0.5460390596689056</v>
       </c>
       <c r="T12">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
     </row>
     <row r="13">
@@ -13231,43 +13231,43 @@
         </is>
       </c>
       <c r="H13">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="I13">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="J13">
-        <v>0.0138494055627222</v>
+        <v>0.01013807726876701</v>
       </c>
       <c r="K13">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="L13">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="M13">
-        <v>-0.793476231018071</v>
+        <v>-0.8619565639887226</v>
       </c>
       <c r="N13">
-        <v>-0.7360172646291882</v>
+        <v>-0.7876843424006484</v>
       </c>
       <c r="O13">
-        <v>-0.6423676349649825</v>
+        <v>-0.6722046376942312</v>
       </c>
       <c r="P13">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="Q13">
-        <v>-0.3950190029311372</v>
+        <v>-0.4083738360338057</v>
       </c>
       <c r="R13">
-        <v>-0.2624236899512734</v>
+        <v>-0.2757117741559034</v>
       </c>
       <c r="S13">
-        <v>-0.1853170997108407</v>
+        <v>-0.1913649839674343</v>
       </c>
       <c r="T13">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
     </row>
     <row r="14">
@@ -13301,43 +13301,43 @@
         </is>
       </c>
       <c r="H14">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I14">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J14">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K14">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L14">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M14">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N14">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O14">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P14">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q14">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R14">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S14">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T14">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="15">
@@ -13371,43 +13371,43 @@
         </is>
       </c>
       <c r="H15">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="I15">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="J15">
-        <v>0.1084019016706564</v>
+        <v>0.07701312410586839</v>
       </c>
       <c r="K15">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="L15">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="M15">
-        <v>-3.488032961964862</v>
+        <v>-3.387966630833503</v>
       </c>
       <c r="N15">
-        <v>-3.003823218096905</v>
+        <v>-2.975243907002977</v>
       </c>
       <c r="O15">
-        <v>-2.290316942476073</v>
+        <v>-2.349070501240922</v>
       </c>
       <c r="P15">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="Q15">
-        <v>-0.9999871789526356</v>
+        <v>-0.9754761953429016</v>
       </c>
       <c r="R15">
-        <v>-0.2572257762999619</v>
+        <v>-0.183671580782594</v>
       </c>
       <c r="S15">
-        <v>0.03687330688384052</v>
+        <v>0.04702015061722756</v>
       </c>
       <c r="T15">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
     </row>
     <row r="16">
@@ -13441,43 +13441,43 @@
         </is>
       </c>
       <c r="H16">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I16">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J16">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K16">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L16">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M16">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N16">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O16">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P16">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q16">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R16">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S16">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T16">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="17">
@@ -13511,43 +13511,43 @@
         </is>
       </c>
       <c r="H17">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I17">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J17">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K17">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L17">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M17">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N17">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O17">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P17">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q17">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R17">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S17">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T17">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="18">
@@ -13581,43 +13581,43 @@
         </is>
       </c>
       <c r="H18">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="I18">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="J18">
-        <v>0.004489188844228981</v>
+        <v>0.002401968778905081</v>
       </c>
       <c r="K18">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="L18">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="M18">
-        <v>-0.3311505668231341</v>
+        <v>-0.3207942158070026</v>
       </c>
       <c r="N18">
-        <v>-0.2733669922777434</v>
+        <v>-0.2750567385371742</v>
       </c>
       <c r="O18">
-        <v>-0.1881028706283962</v>
+        <v>-0.1909895861441369</v>
       </c>
       <c r="P18">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="Q18">
-        <v>-0.01150899139302317</v>
+        <v>-0.01958741750834391</v>
       </c>
       <c r="R18">
-        <v>0.05620358718629397</v>
+        <v>0.05288336647867456</v>
       </c>
       <c r="S18">
-        <v>0.09790972252884569</v>
+        <v>0.09529479881860209</v>
       </c>
       <c r="T18">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
     </row>
     <row r="19">
@@ -13651,43 +13651,43 @@
         </is>
       </c>
       <c r="H19">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="I19">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="J19">
-        <v>0.02637162723743947</v>
+        <v>0.01807548370186413</v>
       </c>
       <c r="K19">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="L19">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="M19">
-        <v>0.09536507547659817</v>
+        <v>0.1120212086109604</v>
       </c>
       <c r="N19">
-        <v>0.2182271469328651</v>
+        <v>0.2147962563771071</v>
       </c>
       <c r="O19">
-        <v>0.3848421882080577</v>
+        <v>0.3671732564636359</v>
       </c>
       <c r="P19">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="Q19">
-        <v>0.716696337758487</v>
+        <v>0.7070879191567029</v>
       </c>
       <c r="R19">
-        <v>0.8442323233560615</v>
+        <v>0.8586412762319757</v>
       </c>
       <c r="S19">
-        <v>0.9268458555843748</v>
+        <v>0.9394946108012314</v>
       </c>
       <c r="T19">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
     </row>
     <row r="20">
@@ -13721,43 +13721,43 @@
         </is>
       </c>
       <c r="H20">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="I20">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="J20">
-        <v>0.00477873489985893</v>
+        <v>0.004006584006451343</v>
       </c>
       <c r="K20">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="L20">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="M20">
-        <v>-0.3046267419691921</v>
+        <v>-0.3268116841121991</v>
       </c>
       <c r="N20">
-        <v>-0.2621410833031751</v>
+        <v>-0.283057820858777</v>
       </c>
       <c r="O20">
-        <v>-0.1948690341940331</v>
+        <v>-0.2106015902179914</v>
       </c>
       <c r="P20">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="Q20">
-        <v>-0.04023992026320443</v>
+        <v>-0.04965583352737096</v>
       </c>
       <c r="R20">
-        <v>0.02516573387752361</v>
+        <v>0.025814225589536</v>
       </c>
       <c r="S20">
-        <v>0.0687494092616685</v>
+        <v>0.06749840563798652</v>
       </c>
       <c r="T20">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
     </row>
     <row r="21">
@@ -13791,43 +13791,43 @@
         </is>
       </c>
       <c r="H21">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="I21">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="J21">
-        <v>0.005808229748890053</v>
+        <v>0.004336999041612884</v>
       </c>
       <c r="K21">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="L21">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="M21">
-        <v>-0.4993147198083546</v>
+        <v>-0.508395418766707</v>
       </c>
       <c r="N21">
-        <v>-0.4494023760354909</v>
+        <v>-0.4551259496182919</v>
       </c>
       <c r="O21">
-        <v>-0.3806903742159381</v>
+        <v>-0.3729647263001437</v>
       </c>
       <c r="P21">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="Q21">
-        <v>-0.2172628751729367</v>
+        <v>-0.2057689564853515</v>
       </c>
       <c r="R21">
-        <v>-0.1437441682113862</v>
+        <v>-0.1312028242246061</v>
       </c>
       <c r="S21">
-        <v>-0.1066270697579693</v>
+        <v>-0.08836986486702653</v>
       </c>
       <c r="T21">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
     </row>
     <row r="22">
@@ -13861,43 +13861,43 @@
         </is>
       </c>
       <c r="H22">
-        <v>0.9183909914910773</v>
+        <v>0.9350824013936898</v>
       </c>
       <c r="I22">
-        <v>0.1304830711675759</v>
+        <v>0.1287839575270144</v>
       </c>
       <c r="J22">
-        <v>0.007629190739139556</v>
+        <v>0.004911631260971691</v>
       </c>
       <c r="K22">
-        <v>0.9188769232333426</v>
+        <v>0.9339599256730006</v>
       </c>
       <c r="L22">
-        <v>0.6586142205919907</v>
+        <v>0.6837604478264198</v>
       </c>
       <c r="M22">
-        <v>0.6973144818432745</v>
+        <v>0.7256969263309898</v>
       </c>
       <c r="N22">
-        <v>0.7525626104506297</v>
+        <v>0.7721319863560734</v>
       </c>
       <c r="O22">
-        <v>0.835069406160258</v>
+        <v>0.8480878806056904</v>
       </c>
       <c r="P22">
-        <v>0.9188769232333426</v>
+        <v>0.9339599256730006</v>
       </c>
       <c r="Q22">
-        <v>1.006385161414666</v>
+        <v>1.022096874431145</v>
       </c>
       <c r="R22">
-        <v>1.083930819456203</v>
+        <v>1.09963839975358</v>
       </c>
       <c r="S22">
-        <v>1.134951693682448</v>
+        <v>1.149915295602883</v>
       </c>
       <c r="T22">
-        <v>1.172675806558851</v>
+        <v>1.188425484603933</v>
       </c>
     </row>
     <row r="23">
@@ -13931,43 +13931,43 @@
         </is>
       </c>
       <c r="H23">
-        <v>-0.4065596936517923</v>
+        <v>-0.3861219822456349</v>
       </c>
       <c r="I23">
-        <v>0.1367732975379721</v>
+        <v>0.1375031246846421</v>
       </c>
       <c r="J23">
-        <v>0.007752243424404085</v>
+        <v>0.005396993969338132</v>
       </c>
       <c r="K23">
-        <v>-0.4059009629105702</v>
+        <v>-0.3844796819927853</v>
       </c>
       <c r="L23">
-        <v>-0.6808653523379501</v>
+        <v>-0.660343584330276</v>
       </c>
       <c r="M23">
-        <v>-0.6290055510176999</v>
+        <v>-0.6127355638936063</v>
       </c>
       <c r="N23">
-        <v>-0.5826112935258686</v>
+        <v>-0.5631256427215817</v>
       </c>
       <c r="O23">
-        <v>-0.4980215224411933</v>
+        <v>-0.4774900201554068</v>
       </c>
       <c r="P23">
-        <v>-0.4059009629105702</v>
+        <v>-0.3844796819927853</v>
       </c>
       <c r="Q23">
-        <v>-0.3120138456327275</v>
+        <v>-0.2959074369696905</v>
       </c>
       <c r="R23">
-        <v>-0.2362582856643825</v>
+        <v>-0.2133831762162299</v>
       </c>
       <c r="S23">
-        <v>-0.1875672023811518</v>
+        <v>-0.1617123972455172</v>
       </c>
       <c r="T23">
-        <v>-0.13768853671991</v>
+        <v>-0.1103279673395892</v>
       </c>
     </row>
     <row r="24">
@@ -14001,43 +14001,43 @@
         </is>
       </c>
       <c r="H24">
-        <v>-0.1889578831058645</v>
+        <v>-0.1831147261014914</v>
       </c>
       <c r="I24">
-        <v>0.1327116504290296</v>
+        <v>0.1350369720875784</v>
       </c>
       <c r="J24">
-        <v>0.004988553944890132</v>
+        <v>0.003915876801680832</v>
       </c>
       <c r="K24">
-        <v>-0.1854118738502842</v>
+        <v>-0.1785893086645667</v>
       </c>
       <c r="L24">
-        <v>-0.4602265954673859</v>
+        <v>-0.4649684790586853</v>
       </c>
       <c r="M24">
-        <v>-0.4109149079112364</v>
+        <v>-0.4154883456029336</v>
       </c>
       <c r="N24">
-        <v>-0.3562558322924651</v>
+        <v>-0.358318296277535</v>
       </c>
       <c r="O24">
-        <v>-0.2767524515129072</v>
+        <v>-0.2698399395404846</v>
       </c>
       <c r="P24">
-        <v>-0.1854118738502842</v>
+        <v>-0.1785893086645667</v>
       </c>
       <c r="Q24">
-        <v>-0.09630601969289393</v>
+        <v>-0.09008199488237223</v>
       </c>
       <c r="R24">
-        <v>-0.02334182334123727</v>
+        <v>-0.01445770825028103</v>
       </c>
       <c r="S24">
-        <v>0.02185289638685428</v>
+        <v>0.03175994551138536</v>
       </c>
       <c r="T24">
-        <v>0.0567593032052706</v>
+        <v>0.06508679198580132</v>
       </c>
     </row>
     <row r="25">
@@ -14071,43 +14071,43 @@
         </is>
       </c>
       <c r="H25">
-        <v>0.4928832352681846</v>
+        <v>0.5216747421585012</v>
       </c>
       <c r="I25">
-        <v>0.2081492105235483</v>
+        <v>0.1656690180157772</v>
       </c>
       <c r="J25">
-        <v>0.142336995204372</v>
+        <v>0.06199340762075325</v>
       </c>
       <c r="K25">
-        <v>0.4948766498617353</v>
+        <v>0.4970093760277954</v>
       </c>
       <c r="L25">
-        <v>0.194505971157467</v>
+        <v>0.2544938193727065</v>
       </c>
       <c r="M25">
-        <v>0.214159402191094</v>
+        <v>0.2818463068147971</v>
       </c>
       <c r="N25">
-        <v>0.2338548175674627</v>
+        <v>0.3183431310005265</v>
       </c>
       <c r="O25">
-        <v>0.3454576614088294</v>
+        <v>0.4034339590777929</v>
       </c>
       <c r="P25">
-        <v>0.4948766498617353</v>
+        <v>0.4970093760277954</v>
       </c>
       <c r="Q25">
-        <v>0.5778643295666729</v>
+        <v>0.621124205496744</v>
       </c>
       <c r="R25">
-        <v>0.7787218439451356</v>
+        <v>0.7744348303172901</v>
       </c>
       <c r="S25">
-        <v>0.9380251412749596</v>
+        <v>0.8405695748132813</v>
       </c>
       <c r="T25">
-        <v>1.018700735436573</v>
+        <v>0.867919380982383</v>
       </c>
     </row>
   </sheetData>
